--- a/research/traditional_assets/database/data/croatia/croatia_recreation.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_recreation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09899509739688327</v>
+        <v>0.09885380622156888</v>
       </c>
       <c r="C2">
-        <v>106.7207596063693</v>
+        <v>105.7713163912381</v>
       </c>
       <c r="D2">
-        <v>87.22075960636926</v>
+        <v>87.34061639123814</v>
       </c>
       <c r="E2">
-        <v>-8.33</v>
+        <v>-7.2607</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.0693</v>
       </c>
       <c r="G2">
         <v>19.5</v>
@@ -1451,28 +1451,28 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05378578999999999</v>
       </c>
       <c r="N2">
-        <v>1.799999999999999</v>
+        <v>1.746214209999999</v>
       </c>
       <c r="O2">
-        <v>0.3239999999999998</v>
+        <v>0.3143185577999998</v>
       </c>
       <c r="P2">
-        <v>1.475999999999999</v>
+        <v>1.431895652199999</v>
       </c>
       <c r="Q2">
-        <v>11.876</v>
+        <v>11.8318956522</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09899509739688327</v>
+        <v>0.09943570325410997</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.9043750110745971</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>33.4660883478703</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09885380622156888</v>
+        <v>0.0987125150462545</v>
       </c>
       <c r="C3">
-        <v>105.7713163912381</v>
+        <v>104.8222030383338</v>
       </c>
       <c r="D3">
-        <v>87.34061639123814</v>
+        <v>87.46080303833379</v>
       </c>
       <c r="E3">
-        <v>-7.2607</v>
+        <v>-6.1914</v>
       </c>
       <c r="F3">
-        <v>1.0693</v>
+        <v>2.1386</v>
       </c>
       <c r="G3">
         <v>19.5</v>
@@ -1533,28 +1533,28 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M3">
-        <v>0.05378578999999999</v>
+        <v>0.10757158</v>
       </c>
       <c r="N3">
-        <v>1.746214209999999</v>
+        <v>1.692428419999999</v>
       </c>
       <c r="O3">
-        <v>0.3143185577999998</v>
+        <v>0.3046371155999998</v>
       </c>
       <c r="P3">
-        <v>1.431895652199999</v>
+        <v>1.387791304399999</v>
       </c>
       <c r="Q3">
-        <v>11.8318956522</v>
+        <v>11.7877913044</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09943570325410997</v>
+        <v>0.09988530106760662</v>
       </c>
       <c r="T3">
-        <v>0.9043750110745971</v>
+        <v>0.9119558761120846</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>33.4660883478703</v>
+        <v>16.73304417393516</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0987125150462545</v>
+        <v>0.0986081238709401</v>
       </c>
       <c r="C4">
-        <v>104.8222030383338</v>
+        <v>103.8419140925586</v>
       </c>
       <c r="D4">
-        <v>87.46080303833379</v>
+        <v>87.54981409255858</v>
       </c>
       <c r="E4">
-        <v>-6.1914</v>
+        <v>-5.122100000000001</v>
       </c>
       <c r="F4">
-        <v>2.1386</v>
+        <v>3.2079</v>
       </c>
       <c r="G4">
         <v>19.5</v>
@@ -1615,45 +1615,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M4">
-        <v>0.10757158</v>
+        <v>0.16616922</v>
       </c>
       <c r="N4">
-        <v>1.692428419999999</v>
+        <v>1.633830779999999</v>
       </c>
       <c r="O4">
-        <v>0.3046371155999998</v>
+        <v>0.2940895403999998</v>
       </c>
       <c r="P4">
-        <v>1.387791304399999</v>
+        <v>1.339741239599999</v>
       </c>
       <c r="Q4">
-        <v>11.7877913044</v>
+        <v>11.7397412396</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09988530106760662</v>
+        <v>0.1003441689391135</v>
       </c>
       <c r="T4">
-        <v>0.9119558761120846</v>
+        <v>0.9196930476451906</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.18</v>
       </c>
       <c r="W4">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>16.73304417393516</v>
+        <v>10.83233104181388</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0986081238709401</v>
+        <v>0.09853489269562571</v>
       </c>
       <c r="C5">
-        <v>103.8419140925586</v>
+        <v>102.8351642059232</v>
       </c>
       <c r="D5">
-        <v>87.54981409255858</v>
+        <v>87.61236420592319</v>
       </c>
       <c r="E5">
-        <v>-5.122100000000001</v>
+        <v>-4.0528</v>
       </c>
       <c r="F5">
-        <v>3.2079</v>
+        <v>4.2772</v>
       </c>
       <c r="G5">
         <v>19.5</v>
@@ -1697,45 +1697,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M5">
-        <v>0.16616922</v>
+        <v>0.2288302</v>
       </c>
       <c r="N5">
-        <v>1.633830779999999</v>
+        <v>1.571169799999999</v>
       </c>
       <c r="O5">
-        <v>0.2940895403999998</v>
+        <v>0.2828105639999998</v>
       </c>
       <c r="P5">
-        <v>1.339741239599999</v>
+        <v>1.288359235999999</v>
       </c>
       <c r="Q5">
-        <v>11.7397412396</v>
+        <v>11.688359236</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1003441689391135</v>
+        <v>0.1008125965579434</v>
       </c>
       <c r="T5">
-        <v>0.9196930476451906</v>
+        <v>0.9275914102519028</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.18</v>
       </c>
       <c r="W5">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>10.83233104181388</v>
+        <v>7.866094597653627</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09853489269562571</v>
+        <v>0.09845264152031132</v>
       </c>
       <c r="C6">
-        <v>102.8351642059232</v>
+        <v>101.8362253708492</v>
       </c>
       <c r="D6">
-        <v>87.61236420592319</v>
+        <v>87.68272537084923</v>
       </c>
       <c r="E6">
-        <v>-4.0528</v>
+        <v>-2.9835</v>
       </c>
       <c r="F6">
-        <v>4.2772</v>
+        <v>5.3465</v>
       </c>
       <c r="G6">
         <v>19.5</v>
@@ -1779,45 +1779,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M6">
-        <v>0.2288302</v>
+        <v>0.29031495</v>
       </c>
       <c r="N6">
-        <v>1.571169799999999</v>
+        <v>1.509685049999999</v>
       </c>
       <c r="O6">
-        <v>0.2828105639999998</v>
+        <v>0.2717433089999998</v>
       </c>
       <c r="P6">
-        <v>1.288359235999999</v>
+        <v>1.237941740999999</v>
       </c>
       <c r="Q6">
-        <v>11.688359236</v>
+        <v>11.637941741</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1008125965579434</v>
+        <v>0.101290885810854</v>
       </c>
       <c r="T6">
-        <v>0.9275914102519028</v>
+        <v>0.935656054176651</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.18</v>
       </c>
       <c r="W6">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>7.866094597653627</v>
+        <v>6.20016296094982</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09845264152031132</v>
+        <v>0.09839335034499692</v>
       </c>
       <c r="C7">
-        <v>101.8362253708492</v>
+        <v>100.8177157086446</v>
       </c>
       <c r="D7">
-        <v>87.68272537084923</v>
+        <v>87.73351570864459</v>
       </c>
       <c r="E7">
-        <v>-2.9835</v>
+        <v>-1.9142</v>
       </c>
       <c r="F7">
-        <v>5.3465</v>
+        <v>6.4158</v>
       </c>
       <c r="G7">
         <v>19.5</v>
@@ -1861,45 +1861,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M7">
-        <v>0.29031495</v>
+        <v>0.35479374</v>
       </c>
       <c r="N7">
-        <v>1.509685049999999</v>
+        <v>1.445206259999999</v>
       </c>
       <c r="O7">
-        <v>0.2717433089999998</v>
+        <v>0.2601371267999998</v>
       </c>
       <c r="P7">
-        <v>1.237941740999999</v>
+        <v>1.185069133199999</v>
       </c>
       <c r="Q7">
-        <v>11.637941741</v>
+        <v>11.5850691332</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.101290885810854</v>
+        <v>0.1017793514308478</v>
       </c>
       <c r="T7">
-        <v>0.935656054176651</v>
+        <v>0.943892286270011</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.18</v>
       </c>
       <c r="W7">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.20016296094982</v>
+        <v>5.073370234773586</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09839335034499692</v>
+        <v>0.09843655916968254</v>
       </c>
       <c r="C8">
-        <v>100.8177157086446</v>
+        <v>99.71139611079427</v>
       </c>
       <c r="D8">
-        <v>87.73351570864459</v>
+        <v>87.69649611079427</v>
       </c>
       <c r="E8">
-        <v>-1.914200000000001</v>
+        <v>-0.8449000000000018</v>
       </c>
       <c r="F8">
-        <v>6.415799999999999</v>
+        <v>7.485099999999998</v>
       </c>
       <c r="G8">
         <v>19.5</v>
@@ -1943,45 +1943,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M8">
-        <v>0.35479374</v>
+        <v>0.4326387799999999</v>
       </c>
       <c r="N8">
-        <v>1.445206259999999</v>
+        <v>1.367361219999999</v>
       </c>
       <c r="O8">
-        <v>0.2601371267999998</v>
+        <v>0.2461250195999998</v>
       </c>
       <c r="P8">
-        <v>1.185069133199999</v>
+        <v>1.121236200399999</v>
       </c>
       <c r="Q8">
-        <v>11.5850691332</v>
+        <v>11.5212362004</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1017793514308478</v>
+        <v>0.1022783216878307</v>
       </c>
       <c r="T8">
-        <v>0.943892286270011</v>
+        <v>0.952305641634196</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V8">
         <v>0.18</v>
       </c>
       <c r="W8">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>5.073370234773588</v>
+        <v>4.160514690800485</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09843655916968252</v>
+        <v>0.09877004799436814</v>
       </c>
       <c r="C9">
-        <v>99.71139611079428</v>
+        <v>98.35742383240344</v>
       </c>
       <c r="D9">
-        <v>87.69649611079429</v>
+        <v>87.41182383240344</v>
       </c>
       <c r="E9">
-        <v>-0.8449</v>
+        <v>0.2243999999999993</v>
       </c>
       <c r="F9">
-        <v>7.4851</v>
+        <v>8.554399999999999</v>
       </c>
       <c r="G9">
         <v>19.5</v>
@@ -2025,45 +2025,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M9">
-        <v>0.4326387800000001</v>
+        <v>0.5483370399999999</v>
       </c>
       <c r="N9">
-        <v>1.367361219999999</v>
+        <v>1.251662959999999</v>
       </c>
       <c r="O9">
-        <v>0.2461250195999998</v>
+        <v>0.2252993327999998</v>
       </c>
       <c r="P9">
-        <v>1.121236200399999</v>
+        <v>1.026363627199999</v>
       </c>
       <c r="Q9">
-        <v>11.5212362004</v>
+        <v>11.4263636272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1022783216878307</v>
+        <v>0.1027881391243132</v>
       </c>
       <c r="T9">
-        <v>0.952305641634196</v>
+        <v>0.9609018960280371</v>
       </c>
       <c r="U9">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V9">
         <v>0.18</v>
       </c>
       <c r="W9">
-        <v>0.04739600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.160514690800484</v>
+        <v>3.282652581704127</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09877004799436814</v>
+        <v>0.09931755681905376</v>
       </c>
       <c r="C10">
-        <v>98.35742383240344</v>
+        <v>96.824746695443</v>
       </c>
       <c r="D10">
-        <v>87.41182383240344</v>
+        <v>86.948446695443</v>
       </c>
       <c r="E10">
-        <v>0.2243999999999993</v>
+        <v>1.293699999999999</v>
       </c>
       <c r="F10">
-        <v>8.554399999999999</v>
+        <v>9.623699999999999</v>
       </c>
       <c r="G10">
         <v>19.5</v>
@@ -2107,45 +2107,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M10">
-        <v>0.5483370399999999</v>
+        <v>0.69194403</v>
       </c>
       <c r="N10">
-        <v>1.251662959999999</v>
+        <v>1.108055969999999</v>
       </c>
       <c r="O10">
-        <v>0.2252993327999998</v>
+        <v>0.1994500745999998</v>
       </c>
       <c r="P10">
-        <v>1.026363627199999</v>
+        <v>0.908605895399999</v>
       </c>
       <c r="Q10">
-        <v>11.4263636272</v>
+        <v>11.3086058954</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1027881391243132</v>
+        <v>0.1033091613396195</v>
       </c>
       <c r="T10">
-        <v>0.9609018960280371</v>
+        <v>0.9696870790898747</v>
       </c>
       <c r="U10">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V10">
         <v>0.18</v>
       </c>
       <c r="W10">
-        <v>0.052562</v>
+        <v>0.05895800000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.282652581704127</v>
+        <v>2.601366471793967</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09931755681905376</v>
+        <v>0.09967318564373938</v>
       </c>
       <c r="C11">
-        <v>96.824746695443</v>
+        <v>95.45708761685776</v>
       </c>
       <c r="D11">
-        <v>86.948446695443</v>
+        <v>86.65008761685776</v>
       </c>
       <c r="E11">
-        <v>1.293699999999999</v>
+        <v>2.362999999999998</v>
       </c>
       <c r="F11">
-        <v>9.623699999999999</v>
+        <v>10.693</v>
       </c>
       <c r="G11">
         <v>19.5</v>
@@ -2189,45 +2189,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M11">
-        <v>0.69194403</v>
+        <v>0.8105294</v>
       </c>
       <c r="N11">
-        <v>1.108055969999999</v>
+        <v>0.989470599999999</v>
       </c>
       <c r="O11">
-        <v>0.1994500745999998</v>
+        <v>0.1781047079999998</v>
       </c>
       <c r="P11">
-        <v>0.908605895399999</v>
+        <v>0.8113658919999992</v>
       </c>
       <c r="Q11">
-        <v>11.3086058954</v>
+        <v>11.211365892</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1033091613396195</v>
+        <v>0.1038417618263771</v>
       </c>
       <c r="T11">
-        <v>0.9696870790898747</v>
+        <v>0.9786674884419754</v>
       </c>
       <c r="U11">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.18</v>
       </c>
       <c r="W11">
-        <v>0.05895800000000001</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.601366471793967</v>
+        <v>2.220770770313821</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09967318564373938</v>
+        <v>0.09974099446842498</v>
       </c>
       <c r="C12">
-        <v>95.45708761685776</v>
+        <v>94.33113086943214</v>
       </c>
       <c r="D12">
-        <v>86.65008761685776</v>
+        <v>86.59343086943214</v>
       </c>
       <c r="E12">
-        <v>2.363</v>
+        <v>3.4323</v>
       </c>
       <c r="F12">
-        <v>10.693</v>
+        <v>11.7623</v>
       </c>
       <c r="G12">
         <v>19.5</v>
@@ -2271,28 +2271,28 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M12">
-        <v>0.8105294000000001</v>
+        <v>0.89158234</v>
       </c>
       <c r="N12">
-        <v>0.9894705999999989</v>
+        <v>0.9084176599999989</v>
       </c>
       <c r="O12">
-        <v>0.1781047079999998</v>
+        <v>0.1635151787999998</v>
       </c>
       <c r="P12">
-        <v>0.8113658919999991</v>
+        <v>0.7449024811999991</v>
       </c>
       <c r="Q12">
-        <v>11.211365892</v>
+        <v>11.1449024812</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1038417618263771</v>
+        <v>0.1043863308633989</v>
       </c>
       <c r="T12">
-        <v>0.9786674884419754</v>
+        <v>0.9878497047458086</v>
       </c>
       <c r="U12">
         <v>0.07580000000000001</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>2.220770770313821</v>
+        <v>2.01888251846711</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09974099446842498</v>
+        <v>0.1012060832931106</v>
       </c>
       <c r="C13">
-        <v>94.33113086943214</v>
+        <v>92.05553781428274</v>
       </c>
       <c r="D13">
-        <v>86.59343086943214</v>
+        <v>85.38713781428274</v>
       </c>
       <c r="E13">
-        <v>3.4323</v>
+        <v>4.501599999999998</v>
       </c>
       <c r="F13">
-        <v>11.7623</v>
+        <v>12.8316</v>
       </c>
       <c r="G13">
         <v>19.5</v>
@@ -2353,45 +2353,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M13">
-        <v>0.89158234</v>
+        <v>1.154844</v>
       </c>
       <c r="N13">
-        <v>0.9084176599999989</v>
+        <v>0.6451559999999992</v>
       </c>
       <c r="O13">
-        <v>0.1635151787999998</v>
+        <v>0.1161280799999998</v>
       </c>
       <c r="P13">
-        <v>0.7449024811999991</v>
+        <v>0.5290279199999993</v>
       </c>
       <c r="Q13">
-        <v>11.1449024812</v>
+        <v>10.92902792</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1043863308633989</v>
+        <v>0.1049432764694438</v>
       </c>
       <c r="T13">
-        <v>0.9878497047458086</v>
+        <v>0.9972406077838198</v>
       </c>
       <c r="U13">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V13">
         <v>0.18</v>
       </c>
       <c r="W13">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>2.01888251846711</v>
+        <v>1.558652077683219</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1012060832931106</v>
+        <v>0.1079971064376223</v>
       </c>
       <c r="C14">
-        <v>92.05553781428274</v>
+        <v>85.80710722261992</v>
       </c>
       <c r="D14">
-        <v>85.38713781428274</v>
+        <v>80.20800722261993</v>
       </c>
       <c r="E14">
-        <v>4.501599999999998</v>
+        <v>5.5709</v>
       </c>
       <c r="F14">
-        <v>12.8316</v>
+        <v>13.9009</v>
       </c>
       <c r="G14">
         <v>19.5</v>
@@ -2435,45 +2435,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M14">
-        <v>1.154844</v>
+        <v>2.04065212</v>
       </c>
       <c r="N14">
-        <v>0.6451559999999992</v>
+        <v>-0.2406521200000014</v>
       </c>
       <c r="O14">
-        <v>0.1161280799999998</v>
+        <v>-0.04331738160000025</v>
       </c>
       <c r="P14">
-        <v>0.5290279199999993</v>
+        <v>-0.1973347384000011</v>
       </c>
       <c r="Q14">
-        <v>10.92902792</v>
+        <v>10.2026652616</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1049432764694438</v>
+        <v>0.1056817541110787</v>
       </c>
       <c r="T14">
-        <v>0.9972406077838198</v>
+        <v>1.009692401734721</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V14">
-        <v>0.18</v>
+        <v>0.1587727750480076</v>
       </c>
       <c r="W14">
-        <v>0.0738</v>
+        <v>0.1234921566229525</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.558652077683219</v>
+        <v>0.882070972488931</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1079971064376223</v>
+        <v>0.1090071064376223</v>
       </c>
       <c r="C15">
-        <v>85.80710722261992</v>
+        <v>84.0207263685876</v>
       </c>
       <c r="D15">
-        <v>80.20800722261993</v>
+        <v>79.49092636858761</v>
       </c>
       <c r="E15">
-        <v>5.5709</v>
+        <v>6.6402</v>
       </c>
       <c r="F15">
-        <v>13.9009</v>
+        <v>14.9702</v>
       </c>
       <c r="G15">
         <v>19.5</v>
@@ -2517,37 +2517,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M15">
-        <v>2.04065212</v>
+        <v>2.19762536</v>
       </c>
       <c r="N15">
-        <v>-0.2406521200000014</v>
+        <v>-0.3976253600000015</v>
       </c>
       <c r="O15">
-        <v>-0.04331738160000025</v>
+        <v>-0.07157256480000027</v>
       </c>
       <c r="P15">
-        <v>-0.1973347384000011</v>
+        <v>-0.3260527952000012</v>
       </c>
       <c r="Q15">
-        <v>10.2026652616</v>
+        <v>10.0739472048</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1056817541110787</v>
+        <v>0.1063780535774866</v>
       </c>
       <c r="T15">
-        <v>1.009692401734721</v>
+        <v>1.021433011057218</v>
       </c>
       <c r="U15">
         <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.1587727750480076</v>
+        <v>0.1474318625445785</v>
       </c>
       <c r="W15">
-        <v>0.1234921566229525</v>
+        <v>0.1251570025784559</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.882070972488931</v>
+        <v>0.8190659030254359</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1090071064376223</v>
+        <v>0.1184123776094013</v>
       </c>
       <c r="C16">
-        <v>84.0207263685876</v>
+        <v>76.84217533273304</v>
       </c>
       <c r="D16">
-        <v>79.49092636858761</v>
+        <v>73.38167533273304</v>
       </c>
       <c r="E16">
-        <v>6.6402</v>
+        <v>7.7095</v>
       </c>
       <c r="F16">
-        <v>14.9702</v>
+        <v>16.0395</v>
       </c>
       <c r="G16">
         <v>19.5</v>
@@ -2599,45 +2599,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M16">
-        <v>2.19762536</v>
+        <v>3.2207316</v>
       </c>
       <c r="N16">
-        <v>-0.3976253600000015</v>
+        <v>-1.420731600000001</v>
       </c>
       <c r="O16">
-        <v>-0.07157256480000027</v>
+        <v>-0.2557316880000002</v>
       </c>
       <c r="P16">
-        <v>-0.3260527952000012</v>
+        <v>-1.164999912000001</v>
       </c>
       <c r="Q16">
-        <v>10.0739472048</v>
+        <v>9.235000088</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1063780535774866</v>
+        <v>0.1074381144099029</v>
       </c>
       <c r="T16">
-        <v>1.021433011057218</v>
+        <v>1.039307159598055</v>
       </c>
       <c r="U16">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.1474318625445785</v>
+        <v>0.1005982615875225</v>
       </c>
       <c r="W16">
-        <v>0.1251570025784559</v>
+        <v>0.1805998690732255</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.8190659030254359</v>
+        <v>0.5588792310417915</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1184123776094013</v>
+        <v>0.1199623776094013</v>
       </c>
       <c r="C17">
-        <v>76.84217533273304</v>
+        <v>74.85506637507186</v>
       </c>
       <c r="D17">
-        <v>73.38167533273304</v>
+        <v>72.46386637507186</v>
       </c>
       <c r="E17">
-        <v>7.709499999999997</v>
+        <v>8.778799999999999</v>
       </c>
       <c r="F17">
-        <v>16.0395</v>
+        <v>17.1088</v>
       </c>
       <c r="G17">
         <v>19.5</v>
@@ -2681,37 +2681,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M17">
-        <v>3.220731599999999</v>
+        <v>3.43544704</v>
       </c>
       <c r="N17">
-        <v>-1.4207316</v>
+        <v>-1.635447040000001</v>
       </c>
       <c r="O17">
-        <v>-0.2557316880000001</v>
+        <v>-0.2943804672000001</v>
       </c>
       <c r="P17">
-        <v>-1.164999912</v>
+        <v>-1.341066572800001</v>
       </c>
       <c r="Q17">
-        <v>9.235000088</v>
+        <v>9.058933427199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1074381144099029</v>
+        <v>0.1081719014862113</v>
       </c>
       <c r="T17">
-        <v>1.039307159598055</v>
+        <v>1.051679863878984</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.1005982615875225</v>
+        <v>0.09431087023830234</v>
       </c>
       <c r="W17">
-        <v>0.1805998690732255</v>
+        <v>0.1818623772561489</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5588792310417916</v>
+        <v>0.5239492791016795</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1199623776094013</v>
+        <v>0.1275815230936943</v>
       </c>
       <c r="C18">
-        <v>74.85506637507186</v>
+        <v>69.58867317974047</v>
       </c>
       <c r="D18">
-        <v>72.46386637507186</v>
+        <v>68.26677317974047</v>
       </c>
       <c r="E18">
-        <v>8.778799999999999</v>
+        <v>9.848100000000001</v>
       </c>
       <c r="F18">
-        <v>17.1088</v>
+        <v>18.1781</v>
       </c>
       <c r="G18">
         <v>19.5</v>
@@ -2763,45 +2763,45 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M18">
-        <v>3.43544704</v>
+        <v>4.28639598</v>
       </c>
       <c r="N18">
-        <v>-1.635447040000001</v>
+        <v>-2.486395980000001</v>
       </c>
       <c r="O18">
-        <v>-0.2943804672000001</v>
+        <v>-0.4475512764000002</v>
       </c>
       <c r="P18">
-        <v>-1.341066572800001</v>
+        <v>-2.038844703600001</v>
       </c>
       <c r="Q18">
-        <v>9.058933427199999</v>
+        <v>8.3611552964</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1081719014862113</v>
+        <v>0.1090669189550729</v>
       </c>
       <c r="T18">
-        <v>1.051679863878984</v>
+        <v>1.066771144205428</v>
       </c>
       <c r="U18">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.09431087023830234</v>
+        <v>0.07558797682523018</v>
       </c>
       <c r="W18">
-        <v>0.1818623772561489</v>
+        <v>0.2179763550646107</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.5239492791016795</v>
+        <v>0.4199332045846121</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1275815230936943</v>
+        <v>0.1294815230936943</v>
       </c>
       <c r="C19">
-        <v>69.58867317974047</v>
+        <v>67.54739631508346</v>
       </c>
       <c r="D19">
-        <v>68.26677317974047</v>
+        <v>67.29479631508346</v>
       </c>
       <c r="E19">
-        <v>9.848100000000001</v>
+        <v>10.9174</v>
       </c>
       <c r="F19">
-        <v>18.1781</v>
+        <v>19.2474</v>
       </c>
       <c r="G19">
         <v>19.5</v>
@@ -2845,37 +2845,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M19">
-        <v>4.28639598</v>
+        <v>4.538536920000001</v>
       </c>
       <c r="N19">
-        <v>-2.486395980000001</v>
+        <v>-2.738536920000002</v>
       </c>
       <c r="O19">
-        <v>-0.4475512764000002</v>
+        <v>-0.4929366456000004</v>
       </c>
       <c r="P19">
-        <v>-2.038844703600001</v>
+        <v>-2.245600274400002</v>
       </c>
       <c r="Q19">
-        <v>8.3611552964</v>
+        <v>8.154399725599998</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1090669189550729</v>
+        <v>0.109838466747208</v>
       </c>
       <c r="T19">
-        <v>1.066771144205428</v>
+        <v>1.079780548403055</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.07558797682523018</v>
+        <v>0.07138864477938403</v>
       </c>
       <c r="W19">
-        <v>0.2179763550646107</v>
+        <v>0.2189665575610213</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.4199332045846121</v>
+        <v>0.3966035821076891</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1294815230936943</v>
+        <v>0.1313815230936944</v>
       </c>
       <c r="C20">
-        <v>67.54739631508347</v>
+        <v>65.53340876529199</v>
       </c>
       <c r="D20">
-        <v>67.29479631508347</v>
+        <v>66.35010876529199</v>
       </c>
       <c r="E20">
-        <v>10.9174</v>
+        <v>11.9867</v>
       </c>
       <c r="F20">
-        <v>19.2474</v>
+        <v>20.3167</v>
       </c>
       <c r="G20">
         <v>19.5</v>
@@ -2927,37 +2927,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M20">
-        <v>4.53853692</v>
+        <v>4.79067786</v>
       </c>
       <c r="N20">
-        <v>-2.738536920000001</v>
+        <v>-2.990677860000001</v>
       </c>
       <c r="O20">
-        <v>-0.4929366456000002</v>
+        <v>-0.5383220148000001</v>
       </c>
       <c r="P20">
-        <v>-2.245600274400001</v>
+        <v>-2.4523558452</v>
       </c>
       <c r="Q20">
-        <v>8.154399725599999</v>
+        <v>7.9476441548</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1098384667472079</v>
+        <v>0.1106290651021118</v>
       </c>
       <c r="T20">
-        <v>1.079780548403055</v>
+        <v>1.093111172457414</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07138864477938406</v>
+        <v>0.06763134768573227</v>
       </c>
       <c r="W20">
-        <v>0.2189665575610212</v>
+        <v>0.2198525282157043</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3966035821076892</v>
+        <v>0.3757297093651792</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1313815230936944</v>
+        <v>0.1332815230936943</v>
       </c>
       <c r="C21">
-        <v>65.53340876529199</v>
+        <v>63.54557717437319</v>
       </c>
       <c r="D21">
-        <v>66.35010876529199</v>
+        <v>65.43157717437319</v>
       </c>
       <c r="E21">
-        <v>11.9867</v>
+        <v>13.056</v>
       </c>
       <c r="F21">
-        <v>20.3167</v>
+        <v>21.386</v>
       </c>
       <c r="G21">
         <v>19.5</v>
@@ -3009,37 +3009,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M21">
-        <v>4.79067786</v>
+        <v>5.0428188</v>
       </c>
       <c r="N21">
-        <v>-2.990677860000001</v>
+        <v>-3.242818800000001</v>
       </c>
       <c r="O21">
-        <v>-0.5383220148000001</v>
+        <v>-0.5837073840000002</v>
       </c>
       <c r="P21">
-        <v>-2.4523558452</v>
+        <v>-2.659111416000001</v>
       </c>
       <c r="Q21">
-        <v>7.9476441548</v>
+        <v>7.740888583999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1106290651021118</v>
+        <v>0.1114394284158881</v>
       </c>
       <c r="T21">
-        <v>1.093111172457414</v>
+        <v>1.106775062113132</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.06763134768573227</v>
+        <v>0.06424978030144565</v>
       </c>
       <c r="W21">
-        <v>0.2198525282157043</v>
+        <v>0.2206499018049191</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3757297093651792</v>
+        <v>0.3569432238969203</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1332815230936943</v>
+        <v>0.1351815230936944</v>
       </c>
       <c r="C22">
-        <v>63.54557717437319</v>
+        <v>61.58283008877657</v>
       </c>
       <c r="D22">
-        <v>65.43157717437319</v>
+        <v>64.53813008877657</v>
       </c>
       <c r="E22">
-        <v>13.056</v>
+        <v>14.1253</v>
       </c>
       <c r="F22">
-        <v>21.386</v>
+        <v>22.4553</v>
       </c>
       <c r="G22">
         <v>19.5</v>
@@ -3091,37 +3091,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M22">
-        <v>5.0428188</v>
+        <v>5.29495974</v>
       </c>
       <c r="N22">
-        <v>-3.242818800000001</v>
+        <v>-3.494959740000001</v>
       </c>
       <c r="O22">
-        <v>-0.5837073840000002</v>
+        <v>-0.6290927532000002</v>
       </c>
       <c r="P22">
-        <v>-2.659111416000001</v>
+        <v>-2.865866986800001</v>
       </c>
       <c r="Q22">
-        <v>7.740888583999999</v>
+        <v>7.534133013199999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1114394284158881</v>
+        <v>0.1122703072565956</v>
       </c>
       <c r="T22">
-        <v>1.106775062113132</v>
+        <v>1.120784873025956</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.06424978030144565</v>
+        <v>0.06119026695375775</v>
       </c>
       <c r="W22">
-        <v>0.2206499018049191</v>
+        <v>0.2213713350523039</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3569432238969203</v>
+        <v>0.3399459275208765</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1351815230936944</v>
+        <v>0.1370815230936943</v>
       </c>
       <c r="C23">
-        <v>61.58283008877657</v>
+        <v>59.64415378803584</v>
       </c>
       <c r="D23">
-        <v>64.53813008877657</v>
+        <v>63.66875378803584</v>
       </c>
       <c r="E23">
-        <v>14.1253</v>
+        <v>15.1946</v>
       </c>
       <c r="F23">
-        <v>22.4553</v>
+        <v>23.5246</v>
       </c>
       <c r="G23">
         <v>19.5</v>
@@ -3173,37 +3173,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M23">
-        <v>5.294959739999999</v>
+        <v>5.54710068</v>
       </c>
       <c r="N23">
-        <v>-3.494959740000001</v>
+        <v>-3.747100680000001</v>
       </c>
       <c r="O23">
-        <v>-0.6290927532</v>
+        <v>-0.6744781224000002</v>
       </c>
       <c r="P23">
-        <v>-2.8658669868</v>
+        <v>-3.072622557600001</v>
       </c>
       <c r="Q23">
-        <v>7.5341330132</v>
+        <v>7.3273774424</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1122703072565956</v>
+        <v>0.1131224906829622</v>
       </c>
       <c r="T23">
-        <v>1.120784873025956</v>
+        <v>1.135153909859622</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.06119026695375777</v>
+        <v>0.05840889118313242</v>
       </c>
       <c r="W23">
-        <v>0.2213713350523039</v>
+        <v>0.2220271834590174</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3399459275208765</v>
+        <v>0.3244938399062912</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1370815230936943</v>
+        <v>0.1389815230936944</v>
       </c>
       <c r="C24">
-        <v>59.64415378803584</v>
+        <v>57.72858844791752</v>
       </c>
       <c r="D24">
-        <v>63.66875378803584</v>
+        <v>62.82248844791751</v>
       </c>
       <c r="E24">
-        <v>15.1946</v>
+        <v>16.2639</v>
       </c>
       <c r="F24">
-        <v>23.5246</v>
+        <v>24.5939</v>
       </c>
       <c r="G24">
         <v>19.5</v>
@@ -3255,37 +3255,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M24">
-        <v>5.54710068</v>
+        <v>5.79924162</v>
       </c>
       <c r="N24">
-        <v>-3.747100680000001</v>
+        <v>-3.999241620000001</v>
       </c>
       <c r="O24">
-        <v>-0.6744781224000002</v>
+        <v>-0.7198634916000002</v>
       </c>
       <c r="P24">
-        <v>-3.072622557600001</v>
+        <v>-3.279378128400001</v>
       </c>
       <c r="Q24">
-        <v>7.3273774424</v>
+        <v>7.120621871599999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1131224906829622</v>
+        <v>0.1139968087437799</v>
       </c>
       <c r="T24">
-        <v>1.135153909859622</v>
+        <v>1.149896168429228</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.05840889118313242</v>
+        <v>0.05586937417517013</v>
       </c>
       <c r="W24">
-        <v>0.2220271834590174</v>
+        <v>0.2226260015694949</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3244938399062912</v>
+        <v>0.3103854120842785</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1389815230936944</v>
+        <v>0.1408815230936943</v>
       </c>
       <c r="C25">
-        <v>57.72858844791752</v>
+        <v>55.83522460554543</v>
       </c>
       <c r="D25">
-        <v>62.82248844791751</v>
+        <v>61.99842460554543</v>
       </c>
       <c r="E25">
-        <v>16.2639</v>
+        <v>17.3332</v>
       </c>
       <c r="F25">
-        <v>24.5939</v>
+        <v>25.6632</v>
       </c>
       <c r="G25">
         <v>19.5</v>
@@ -3337,37 +3337,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M25">
-        <v>5.79924162</v>
+        <v>6.05138256</v>
       </c>
       <c r="N25">
-        <v>-3.999241620000001</v>
+        <v>-4.251382560000001</v>
       </c>
       <c r="O25">
-        <v>-0.7198634916000002</v>
+        <v>-0.7652488608000002</v>
       </c>
       <c r="P25">
-        <v>-3.279378128400001</v>
+        <v>-3.486133699200001</v>
       </c>
       <c r="Q25">
-        <v>7.120621871599999</v>
+        <v>6.913866300799999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1139968087437799</v>
+        <v>0.1148941351746191</v>
       </c>
       <c r="T25">
-        <v>1.149896168429228</v>
+        <v>1.165026381171718</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.05586937417517013</v>
+        <v>0.05354148358453804</v>
       </c>
       <c r="W25">
-        <v>0.2226260015694949</v>
+        <v>0.2231749181707659</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3103854120842785</v>
+        <v>0.2974526865807668</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1408815230936943</v>
+        <v>0.1427815230936944</v>
       </c>
       <c r="C26">
-        <v>55.83522460554544</v>
+        <v>53.96319989913179</v>
       </c>
       <c r="D26">
-        <v>61.99842460554543</v>
+        <v>61.1956998991318</v>
       </c>
       <c r="E26">
-        <v>17.3332</v>
+        <v>18.4025</v>
       </c>
       <c r="F26">
-        <v>25.6632</v>
+        <v>26.7325</v>
       </c>
       <c r="G26">
         <v>19.5</v>
@@ -3419,37 +3419,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M26">
-        <v>6.05138256</v>
+        <v>6.3035235</v>
       </c>
       <c r="N26">
-        <v>-4.251382560000001</v>
+        <v>-4.503523500000001</v>
       </c>
       <c r="O26">
-        <v>-0.7652488608000001</v>
+        <v>-0.8106342300000001</v>
       </c>
       <c r="P26">
-        <v>-3.486133699200001</v>
+        <v>-3.692889270000001</v>
       </c>
       <c r="Q26">
-        <v>6.9138663008</v>
+        <v>6.70711073</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1148941351746191</v>
+        <v>0.1158153903102807</v>
       </c>
       <c r="T26">
-        <v>1.165026381171717</v>
+        <v>1.180560066254007</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05354148358453805</v>
+        <v>0.05139982424115652</v>
       </c>
       <c r="W26">
-        <v>0.2231749181707659</v>
+        <v>0.2236799214439353</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.297452686580767</v>
+        <v>0.2855545791175362</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1427815230936944</v>
+        <v>0.1446815230936944</v>
       </c>
       <c r="C27">
-        <v>53.96319989913179</v>
+        <v>52.11169605774519</v>
       </c>
       <c r="D27">
-        <v>61.1956998991318</v>
+        <v>60.4134960577452</v>
       </c>
       <c r="E27">
-        <v>18.4025</v>
+        <v>19.4718</v>
       </c>
       <c r="F27">
-        <v>26.7325</v>
+        <v>27.8018</v>
       </c>
       <c r="G27">
         <v>19.5</v>
@@ -3501,37 +3501,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M27">
-        <v>6.3035235</v>
+        <v>6.55566444</v>
       </c>
       <c r="N27">
-        <v>-4.503523500000001</v>
+        <v>-4.755664440000001</v>
       </c>
       <c r="O27">
-        <v>-0.8106342300000001</v>
+        <v>-0.8560195992000001</v>
       </c>
       <c r="P27">
-        <v>-3.692889270000001</v>
+        <v>-3.899644840800001</v>
       </c>
       <c r="Q27">
-        <v>6.70711073</v>
+        <v>6.5003551592</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1158153903102807</v>
+        <v>0.1167615442333926</v>
       </c>
       <c r="T27">
-        <v>1.180560066254007</v>
+        <v>1.196513580662845</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.05139982424115652</v>
+        <v>0.04942290792418896</v>
       </c>
       <c r="W27">
-        <v>0.2236799214439353</v>
+        <v>0.2241460783114762</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2855545791175362</v>
+        <v>0.2745717106899387</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1446815230936944</v>
+        <v>0.1465815230936943</v>
       </c>
       <c r="C28">
-        <v>52.11169605774519</v>
+        <v>50.27993611902566</v>
       </c>
       <c r="D28">
-        <v>60.4134960577452</v>
+        <v>59.65103611902565</v>
       </c>
       <c r="E28">
-        <v>19.4718</v>
+        <v>20.5411</v>
       </c>
       <c r="F28">
-        <v>27.8018</v>
+        <v>28.8711</v>
       </c>
       <c r="G28">
         <v>19.5</v>
@@ -3583,37 +3583,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M28">
-        <v>6.55566444</v>
+        <v>6.80780538</v>
       </c>
       <c r="N28">
-        <v>-4.755664440000001</v>
+        <v>-5.007805380000001</v>
       </c>
       <c r="O28">
-        <v>-0.8560195992000001</v>
+        <v>-0.9014049684000001</v>
       </c>
       <c r="P28">
-        <v>-3.899644840800001</v>
+        <v>-4.106400411600001</v>
       </c>
       <c r="Q28">
-        <v>6.5003551592</v>
+        <v>6.293599588399999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1167615442333926</v>
+        <v>0.1177336201817952</v>
       </c>
       <c r="T28">
-        <v>1.196513580662845</v>
+        <v>1.212904177658227</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04942290792418896</v>
+        <v>0.04759242985292271</v>
       </c>
       <c r="W28">
-        <v>0.2241460783114762</v>
+        <v>0.2245777050406808</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2745717106899387</v>
+        <v>0.2644023880717928</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1465815230936943</v>
+        <v>0.1484815230936943</v>
       </c>
       <c r="C29">
-        <v>50.27993611902566</v>
+        <v>48.46718185495992</v>
       </c>
       <c r="D29">
-        <v>59.65103611902565</v>
+        <v>58.90758185495992</v>
       </c>
       <c r="E29">
-        <v>20.5411</v>
+        <v>21.6104</v>
       </c>
       <c r="F29">
-        <v>28.8711</v>
+        <v>29.9404</v>
       </c>
       <c r="G29">
         <v>19.5</v>
@@ -3665,37 +3665,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M29">
-        <v>6.80780538</v>
+        <v>7.059946320000001</v>
       </c>
       <c r="N29">
-        <v>-5.007805380000001</v>
+        <v>-5.259946320000002</v>
       </c>
       <c r="O29">
-        <v>-0.9014049684000001</v>
+        <v>-0.9467903376000003</v>
       </c>
       <c r="P29">
-        <v>-4.106400411600001</v>
+        <v>-4.313155982400001</v>
       </c>
       <c r="Q29">
-        <v>6.293599588399999</v>
+        <v>6.086844017599999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1177336201817952</v>
+        <v>0.1187326982398757</v>
       </c>
       <c r="T29">
-        <v>1.212904177658227</v>
+        <v>1.229750069014591</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.04759242985292271</v>
+        <v>0.04589270021531831</v>
       </c>
       <c r="W29">
-        <v>0.2245777050406808</v>
+        <v>0.2249785012892279</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2644023880717928</v>
+        <v>0.2549594456406573</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1484815230936943</v>
+        <v>0.1503815230936943</v>
       </c>
       <c r="C30">
-        <v>48.46718185495992</v>
+        <v>46.67273138778861</v>
       </c>
       <c r="D30">
-        <v>58.90758185495992</v>
+        <v>58.18243138778861</v>
       </c>
       <c r="E30">
-        <v>21.6104</v>
+        <v>22.6797</v>
       </c>
       <c r="F30">
-        <v>29.9404</v>
+        <v>31.0097</v>
       </c>
       <c r="G30">
         <v>19.5</v>
@@ -3747,37 +3747,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M30">
-        <v>7.059946320000001</v>
+        <v>7.312087260000001</v>
       </c>
       <c r="N30">
-        <v>-5.259946320000002</v>
+        <v>-5.512087260000002</v>
       </c>
       <c r="O30">
-        <v>-0.9467903376000003</v>
+        <v>-0.9921757068000003</v>
       </c>
       <c r="P30">
-        <v>-4.313155982400001</v>
+        <v>-4.519911553200002</v>
       </c>
       <c r="Q30">
-        <v>6.086844017599999</v>
+        <v>5.880088446799999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1187326982398757</v>
+        <v>0.1197599193418458</v>
       </c>
       <c r="T30">
-        <v>1.229750069014591</v>
+        <v>1.247070492521839</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04589270021531831</v>
+        <v>0.04431019331134183</v>
       </c>
       <c r="W30">
-        <v>0.2249785012892279</v>
+        <v>0.2253516564171856</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2549594456406573</v>
+        <v>0.2461677406185657</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1503815230936943</v>
+        <v>0.1522815230936943</v>
       </c>
       <c r="C31">
-        <v>46.67273138778863</v>
+        <v>44.8959169798607</v>
       </c>
       <c r="D31">
-        <v>58.18243138778862</v>
+        <v>57.47491697986069</v>
       </c>
       <c r="E31">
-        <v>22.6797</v>
+        <v>23.749</v>
       </c>
       <c r="F31">
-        <v>31.0097</v>
+        <v>32.07899999999999</v>
       </c>
       <c r="G31">
         <v>19.5</v>
@@ -3829,37 +3829,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M31">
-        <v>7.312087259999999</v>
+        <v>7.564228199999999</v>
       </c>
       <c r="N31">
-        <v>-5.51208726</v>
+        <v>-5.7642282</v>
       </c>
       <c r="O31">
-        <v>-0.9921757068</v>
+        <v>-1.037561076</v>
       </c>
       <c r="P31">
-        <v>-4.5199115532</v>
+        <v>-4.726667124</v>
       </c>
       <c r="Q31">
-        <v>5.8800884468</v>
+        <v>5.673332876000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1197599193418458</v>
+        <v>0.1208164896181579</v>
       </c>
       <c r="T31">
-        <v>1.247070492521838</v>
+        <v>1.26488578527215</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04431019331134183</v>
+        <v>0.04283318686763044</v>
       </c>
       <c r="W31">
-        <v>0.2253516564171856</v>
+        <v>0.2256999345366127</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2461677406185657</v>
+        <v>0.2379621492646136</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1522815230936943</v>
+        <v>0.1541815230936943</v>
       </c>
       <c r="C32">
-        <v>44.8959169798607</v>
+        <v>43.13610298280637</v>
       </c>
       <c r="D32">
-        <v>57.47491697986069</v>
+        <v>56.78440298280636</v>
       </c>
       <c r="E32">
-        <v>23.749</v>
+        <v>24.8183</v>
       </c>
       <c r="F32">
-        <v>32.07899999999999</v>
+        <v>33.1483</v>
       </c>
       <c r="G32">
         <v>19.5</v>
@@ -3911,37 +3911,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M32">
-        <v>7.564228199999999</v>
+        <v>7.81636914</v>
       </c>
       <c r="N32">
-        <v>-5.7642282</v>
+        <v>-6.016369140000001</v>
       </c>
       <c r="O32">
-        <v>-1.037561076</v>
+        <v>-1.0829464452</v>
       </c>
       <c r="P32">
-        <v>-4.726667124</v>
+        <v>-4.933422694800001</v>
       </c>
       <c r="Q32">
-        <v>5.673332876000001</v>
+        <v>5.4665773052</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1208164896181579</v>
+        <v>0.1219036851198703</v>
       </c>
       <c r="T32">
-        <v>1.26488578527215</v>
+        <v>1.283217463319573</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.04283318686763044</v>
+        <v>0.041451471162223</v>
       </c>
       <c r="W32">
-        <v>0.2256999345366127</v>
+        <v>0.2260257430999478</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2379621492646136</v>
+        <v>0.2302859509012389</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1541815230936943</v>
+        <v>0.1560815230936943</v>
       </c>
       <c r="C33">
-        <v>43.13610298280637</v>
+        <v>41.39268393278912</v>
       </c>
       <c r="D33">
-        <v>56.78440298280636</v>
+        <v>56.11028393278912</v>
       </c>
       <c r="E33">
-        <v>24.8183</v>
+        <v>25.8876</v>
       </c>
       <c r="F33">
-        <v>33.1483</v>
+        <v>34.2176</v>
       </c>
       <c r="G33">
         <v>19.5</v>
@@ -3993,37 +3993,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M33">
-        <v>7.81636914</v>
+        <v>8.068510079999999</v>
       </c>
       <c r="N33">
-        <v>-6.016369140000001</v>
+        <v>-6.26851008</v>
       </c>
       <c r="O33">
-        <v>-1.0829464452</v>
+        <v>-1.1283318144</v>
       </c>
       <c r="P33">
-        <v>-4.933422694800001</v>
+        <v>-5.1401782656</v>
       </c>
       <c r="Q33">
-        <v>5.4665773052</v>
+        <v>5.2598217344</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1219036851198703</v>
+        <v>0.1230228569598684</v>
       </c>
       <c r="T33">
-        <v>1.283217463319573</v>
+        <v>1.30208830836839</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.041451471162223</v>
+        <v>0.04015611268840353</v>
       </c>
       <c r="W33">
-        <v>0.2260257430999478</v>
+        <v>0.2263311886280744</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2302859509012389</v>
+        <v>0.2230895149355752</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1560815230936943</v>
+        <v>0.1579815230936943</v>
       </c>
       <c r="C34">
-        <v>41.39268393278912</v>
+        <v>39.66508277983983</v>
       </c>
       <c r="D34">
-        <v>56.11028393278912</v>
+        <v>55.45198277983983</v>
       </c>
       <c r="E34">
-        <v>25.8876</v>
+        <v>26.9569</v>
       </c>
       <c r="F34">
-        <v>34.2176</v>
+        <v>35.2869</v>
       </c>
       <c r="G34">
         <v>19.5</v>
@@ -4075,37 +4075,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M34">
-        <v>8.068510079999999</v>
+        <v>8.32065102</v>
       </c>
       <c r="N34">
-        <v>-6.26851008</v>
+        <v>-6.520651020000001</v>
       </c>
       <c r="O34">
-        <v>-1.1283318144</v>
+        <v>-1.1737171836</v>
       </c>
       <c r="P34">
-        <v>-5.1401782656</v>
+        <v>-5.346933836400001</v>
       </c>
       <c r="Q34">
-        <v>5.2598217344</v>
+        <v>5.0530661636</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1230228569598684</v>
+        <v>0.1241754369144933</v>
       </c>
       <c r="T34">
-        <v>1.30208830836839</v>
+        <v>1.321522462224635</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04015611268840353</v>
+        <v>0.03893926078875494</v>
       </c>
       <c r="W34">
-        <v>0.2263311886280744</v>
+        <v>0.2266181223060116</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2230895149355752</v>
+        <v>0.2163292266041942</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1579815230936943</v>
+        <v>0.1598815230936944</v>
       </c>
       <c r="C35">
-        <v>39.66508277983983</v>
+        <v>37.9527492403891</v>
       </c>
       <c r="D35">
-        <v>55.45198277983983</v>
+        <v>54.8089492403891</v>
       </c>
       <c r="E35">
-        <v>26.9569</v>
+        <v>28.0262</v>
       </c>
       <c r="F35">
-        <v>35.2869</v>
+        <v>36.3562</v>
       </c>
       <c r="G35">
         <v>19.5</v>
@@ -4157,37 +4157,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M35">
-        <v>8.32065102</v>
+        <v>8.57279196</v>
       </c>
       <c r="N35">
-        <v>-6.520651020000001</v>
+        <v>-6.772791960000001</v>
       </c>
       <c r="O35">
-        <v>-1.1737171836</v>
+        <v>-1.2191025528</v>
       </c>
       <c r="P35">
-        <v>-5.346933836400001</v>
+        <v>-5.553689407200001</v>
       </c>
       <c r="Q35">
-        <v>5.0530661636</v>
+        <v>4.846310592799999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1241754369144933</v>
+        <v>0.1253629435344099</v>
       </c>
       <c r="T35">
-        <v>1.321522462224635</v>
+        <v>1.341545529834099</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03893926078875494</v>
+        <v>0.03779398841261509</v>
       </c>
       <c r="W35">
-        <v>0.2266181223060116</v>
+        <v>0.2268881775323054</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2163292266041942</v>
+        <v>0.209966602292306</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1598815230936944</v>
+        <v>0.1617815230936943</v>
       </c>
       <c r="C36">
-        <v>37.9527492403891</v>
+        <v>36.25515826311198</v>
       </c>
       <c r="D36">
-        <v>54.8089492403891</v>
+        <v>54.18065826311199</v>
       </c>
       <c r="E36">
-        <v>28.0262</v>
+        <v>29.0955</v>
       </c>
       <c r="F36">
-        <v>36.3562</v>
+        <v>37.4255</v>
       </c>
       <c r="G36">
         <v>19.5</v>
@@ -4239,37 +4239,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M36">
-        <v>8.57279196</v>
+        <v>8.8249329</v>
       </c>
       <c r="N36">
-        <v>-6.772791960000001</v>
+        <v>-7.024932900000001</v>
       </c>
       <c r="O36">
-        <v>-1.2191025528</v>
+        <v>-1.264487922</v>
       </c>
       <c r="P36">
-        <v>-5.553689407200001</v>
+        <v>-5.760444978000001</v>
       </c>
       <c r="Q36">
-        <v>4.846310592799999</v>
+        <v>4.639555022</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1253629435344099</v>
+        <v>0.1265869888195547</v>
       </c>
       <c r="T36">
-        <v>1.341545529834099</v>
+        <v>1.362184691831547</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03779398841261509</v>
+        <v>0.03671416017225466</v>
       </c>
       <c r="W36">
-        <v>0.2268881775323054</v>
+        <v>0.2271428010313823</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.209966602292306</v>
+        <v>0.2039675565125258</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1617815230936943</v>
+        <v>0.1636815230936943</v>
       </c>
       <c r="C37">
-        <v>36.25515826311198</v>
+        <v>34.5718085990957</v>
       </c>
       <c r="D37">
-        <v>54.18065826311199</v>
+        <v>53.56660859909571</v>
       </c>
       <c r="E37">
-        <v>29.0955</v>
+        <v>30.16480000000001</v>
       </c>
       <c r="F37">
-        <v>37.4255</v>
+        <v>38.49480000000001</v>
       </c>
       <c r="G37">
         <v>19.5</v>
@@ -4321,37 +4321,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M37">
-        <v>8.8249329</v>
+        <v>9.077073840000002</v>
       </c>
       <c r="N37">
-        <v>-7.024932900000001</v>
+        <v>-7.277073840000003</v>
       </c>
       <c r="O37">
-        <v>-1.264487922</v>
+        <v>-1.309873291200001</v>
       </c>
       <c r="P37">
-        <v>-5.760444978000001</v>
+        <v>-5.967200548800003</v>
       </c>
       <c r="Q37">
-        <v>4.639555022</v>
+        <v>4.432799451199998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1265869888195547</v>
+        <v>0.1278492855198602</v>
       </c>
       <c r="T37">
-        <v>1.362184691831547</v>
+        <v>1.383468827641415</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03671416017225466</v>
+        <v>0.03569432238969202</v>
       </c>
       <c r="W37">
-        <v>0.2271428010313823</v>
+        <v>0.2273832787805106</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2039675565125258</v>
+        <v>0.1983017910538446</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1636815230936943</v>
+        <v>0.1655815230936943</v>
       </c>
       <c r="C38">
-        <v>34.5718085990957</v>
+        <v>32.90222146814665</v>
       </c>
       <c r="D38">
-        <v>53.56660859909571</v>
+        <v>52.96632146814665</v>
       </c>
       <c r="E38">
-        <v>30.1648</v>
+        <v>31.2341</v>
       </c>
       <c r="F38">
-        <v>38.4948</v>
+        <v>39.5641</v>
       </c>
       <c r="G38">
         <v>19.5</v>
@@ -4403,37 +4403,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M38">
-        <v>9.077073840000001</v>
+        <v>9.329214779999999</v>
       </c>
       <c r="N38">
-        <v>-7.277073840000002</v>
+        <v>-7.52921478</v>
       </c>
       <c r="O38">
-        <v>-1.3098732912</v>
+        <v>-1.3552586604</v>
       </c>
       <c r="P38">
-        <v>-5.967200548800001</v>
+        <v>-6.1739561196</v>
       </c>
       <c r="Q38">
-        <v>4.432799451199999</v>
+        <v>4.226043880400001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1278492855198602</v>
+        <v>0.1291516551312865</v>
       </c>
       <c r="T38">
-        <v>1.383468827641414</v>
+        <v>1.405428650302389</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03569432238969203</v>
+        <v>0.03472961097375441</v>
       </c>
       <c r="W38">
-        <v>0.2273832787805106</v>
+        <v>0.2276107577323887</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1983017910538446</v>
+        <v>0.1929422831875245</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1655815230936943</v>
+        <v>0.1674815230936944</v>
       </c>
       <c r="C39">
-        <v>32.90222146814665</v>
+        <v>31.24593931377885</v>
       </c>
       <c r="D39">
-        <v>52.96632146814665</v>
+        <v>52.37933931377884</v>
       </c>
       <c r="E39">
-        <v>31.2341</v>
+        <v>32.3034</v>
       </c>
       <c r="F39">
-        <v>39.5641</v>
+        <v>40.63339999999999</v>
       </c>
       <c r="G39">
         <v>19.5</v>
@@ -4485,37 +4485,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M39">
-        <v>9.329214779999999</v>
+        <v>9.581355719999999</v>
       </c>
       <c r="N39">
-        <v>-7.52921478</v>
+        <v>-7.781355720000001</v>
       </c>
       <c r="O39">
-        <v>-1.3552586604</v>
+        <v>-1.4006440296</v>
       </c>
       <c r="P39">
-        <v>-6.1739561196</v>
+        <v>-6.3807116904</v>
       </c>
       <c r="Q39">
-        <v>4.226043880400001</v>
+        <v>4.0192883096</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1291516551312865</v>
+        <v>0.1304960366656621</v>
       </c>
       <c r="T39">
-        <v>1.405428650302389</v>
+        <v>1.428096854339525</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03472961097375441</v>
+        <v>0.03381567384286614</v>
       </c>
       <c r="W39">
-        <v>0.2276107577323887</v>
+        <v>0.2278262641078522</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1929422831875245</v>
+        <v>0.1878648546825896</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1674815230936944</v>
+        <v>0.1693815230936943</v>
       </c>
       <c r="C40">
-        <v>31.24593931377885</v>
+        <v>29.60252464007944</v>
       </c>
       <c r="D40">
-        <v>52.37933931377884</v>
+        <v>51.80522464007945</v>
       </c>
       <c r="E40">
-        <v>32.3034</v>
+        <v>33.3727</v>
       </c>
       <c r="F40">
-        <v>40.63339999999999</v>
+        <v>41.7027</v>
       </c>
       <c r="G40">
         <v>19.5</v>
@@ -4567,37 +4567,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M40">
-        <v>9.581355719999999</v>
+        <v>9.83349666</v>
       </c>
       <c r="N40">
-        <v>-7.781355720000001</v>
+        <v>-8.033496660000001</v>
       </c>
       <c r="O40">
-        <v>-1.4006440296</v>
+        <v>-1.4460293988</v>
       </c>
       <c r="P40">
-        <v>-6.3807116904</v>
+        <v>-6.5874672612</v>
       </c>
       <c r="Q40">
-        <v>4.0192883096</v>
+        <v>3.8125327388</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1304960366656621</v>
+        <v>0.131884496283132</v>
       </c>
       <c r="T40">
-        <v>1.428096854339525</v>
+        <v>1.451508278181156</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03381567384286614</v>
+        <v>0.03294860528279264</v>
       </c>
       <c r="W40">
-        <v>0.2278262641078522</v>
+        <v>0.2280307188743175</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1878648546825896</v>
+        <v>0.1830478071266258</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1693815230936943</v>
+        <v>0.1712815230936943</v>
       </c>
       <c r="C41">
-        <v>29.60252464007944</v>
+        <v>27.97155892423783</v>
       </c>
       <c r="D41">
-        <v>51.80522464007945</v>
+        <v>51.24355892423783</v>
       </c>
       <c r="E41">
-        <v>33.3727</v>
+        <v>34.442</v>
       </c>
       <c r="F41">
-        <v>41.7027</v>
+        <v>42.772</v>
       </c>
       <c r="G41">
         <v>19.5</v>
@@ -4649,37 +4649,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M41">
-        <v>9.83349666</v>
+        <v>10.0856376</v>
       </c>
       <c r="N41">
-        <v>-8.033496660000001</v>
+        <v>-8.285637600000001</v>
       </c>
       <c r="O41">
-        <v>-1.4460293988</v>
+        <v>-1.491414768</v>
       </c>
       <c r="P41">
-        <v>-6.5874672612</v>
+        <v>-6.794222832000001</v>
       </c>
       <c r="Q41">
-        <v>3.8125327388</v>
+        <v>3.605777167999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.131884496283132</v>
+        <v>0.1333192378878509</v>
       </c>
       <c r="T41">
-        <v>1.451508278181156</v>
+        <v>1.475700082817509</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03294860528279264</v>
+        <v>0.03212489015072283</v>
       </c>
       <c r="W41">
-        <v>0.2280307188743175</v>
+        <v>0.2282249509024596</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1830478071266258</v>
+        <v>0.1784716119484602</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1712815230936943</v>
+        <v>0.1731815230936944</v>
       </c>
       <c r="C42">
-        <v>27.97155892423783</v>
+        <v>26.35264159905709</v>
       </c>
       <c r="D42">
-        <v>51.24355892423783</v>
+        <v>50.69394159905708</v>
       </c>
       <c r="E42">
-        <v>34.442</v>
+        <v>35.5113</v>
       </c>
       <c r="F42">
-        <v>42.772</v>
+        <v>43.8413</v>
       </c>
       <c r="G42">
         <v>19.5</v>
@@ -4731,37 +4731,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M42">
-        <v>10.0856376</v>
+        <v>10.33777854</v>
       </c>
       <c r="N42">
-        <v>-8.285637600000001</v>
+        <v>-8.537778540000001</v>
       </c>
       <c r="O42">
-        <v>-1.491414768</v>
+        <v>-1.5368001372</v>
       </c>
       <c r="P42">
-        <v>-6.794222832000001</v>
+        <v>-7.000978402800001</v>
       </c>
       <c r="Q42">
-        <v>3.605777167999999</v>
+        <v>3.399021597199999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1333192378878509</v>
+        <v>0.1348026148012043</v>
       </c>
       <c r="T42">
-        <v>1.475700082817509</v>
+        <v>1.500711948627975</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03212489015072283</v>
+        <v>0.03134135624460763</v>
       </c>
       <c r="W42">
-        <v>0.2282249509024596</v>
+        <v>0.2284097081975215</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1784716119484602</v>
+        <v>0.1741186458033758</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1731815230936944</v>
+        <v>0.1750815230936943</v>
       </c>
       <c r="C43">
-        <v>26.35264159905709</v>
+        <v>24.74538910024977</v>
       </c>
       <c r="D43">
-        <v>50.69394159905708</v>
+        <v>50.15598910024978</v>
       </c>
       <c r="E43">
-        <v>35.5113</v>
+        <v>36.5806</v>
       </c>
       <c r="F43">
-        <v>43.8413</v>
+        <v>44.9106</v>
       </c>
       <c r="G43">
         <v>19.5</v>
@@ -4813,37 +4813,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M43">
-        <v>10.33777854</v>
+        <v>10.58991948</v>
       </c>
       <c r="N43">
-        <v>-8.537778540000001</v>
+        <v>-8.789919480000002</v>
       </c>
       <c r="O43">
-        <v>-1.5368001372</v>
+        <v>-1.5821855064</v>
       </c>
       <c r="P43">
-        <v>-7.000978402800001</v>
+        <v>-7.207733973600002</v>
       </c>
       <c r="Q43">
-        <v>3.399021597199999</v>
+        <v>3.192266026399999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1348026148012043</v>
+        <v>0.1363371426426044</v>
       </c>
       <c r="T43">
-        <v>1.500711948627975</v>
+        <v>1.526586292569837</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03134135624460763</v>
+        <v>0.03059513347687888</v>
       </c>
       <c r="W43">
-        <v>0.2284097081975215</v>
+        <v>0.2285856675261519</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1741186458033758</v>
+        <v>0.1699729637604382</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1750815230936943</v>
+        <v>0.1769815230936944</v>
       </c>
       <c r="C44">
-        <v>24.74538910024977</v>
+        <v>23.14943397375591</v>
       </c>
       <c r="D44">
-        <v>50.15598910024978</v>
+        <v>49.6293339737559</v>
       </c>
       <c r="E44">
-        <v>36.5806</v>
+        <v>37.6499</v>
       </c>
       <c r="F44">
-        <v>44.9106</v>
+        <v>45.97989999999999</v>
       </c>
       <c r="G44">
         <v>19.5</v>
@@ -4895,37 +4895,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M44">
-        <v>10.58991948</v>
+        <v>10.84206042</v>
       </c>
       <c r="N44">
-        <v>-8.78991948</v>
+        <v>-9.04206042</v>
       </c>
       <c r="O44">
-        <v>-1.5821855064</v>
+        <v>-1.6275708756</v>
       </c>
       <c r="P44">
-        <v>-7.2077339736</v>
+        <v>-7.4144895444</v>
       </c>
       <c r="Q44">
-        <v>3.1922660264</v>
+        <v>2.9855104556</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1363371426426043</v>
+        <v>0.1379255135661588</v>
       </c>
       <c r="T44">
-        <v>1.526586292569837</v>
+        <v>1.553368508228957</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03059513347687888</v>
+        <v>0.02988361874485844</v>
       </c>
       <c r="W44">
-        <v>0.2285856675261519</v>
+        <v>0.2287534426999624</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1699729637604382</v>
+        <v>0.1660201041381024</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1769815230936944</v>
+        <v>0.1788815230936944</v>
       </c>
       <c r="C45">
-        <v>23.14943397375591</v>
+        <v>21.56442403871736</v>
       </c>
       <c r="D45">
-        <v>49.6293339737559</v>
+        <v>49.11362403871736</v>
       </c>
       <c r="E45">
-        <v>37.6499</v>
+        <v>38.7192</v>
       </c>
       <c r="F45">
-        <v>45.97989999999999</v>
+        <v>47.0492</v>
       </c>
       <c r="G45">
         <v>19.5</v>
@@ -4977,37 +4977,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M45">
-        <v>10.84206042</v>
+        <v>11.09420136</v>
       </c>
       <c r="N45">
-        <v>-9.04206042</v>
+        <v>-9.294201360000001</v>
       </c>
       <c r="O45">
-        <v>-1.6275708756</v>
+        <v>-1.6729562448</v>
       </c>
       <c r="P45">
-        <v>-7.4144895444</v>
+        <v>-7.621245115200001</v>
       </c>
       <c r="Q45">
-        <v>2.9855104556</v>
+        <v>2.7787548848</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1379255135661588</v>
+        <v>0.1395706120226974</v>
       </c>
       <c r="T45">
-        <v>1.553368508228957</v>
+        <v>1.581107231590188</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02988361874485844</v>
+        <v>0.02920444559156621</v>
       </c>
       <c r="W45">
-        <v>0.2287534426999624</v>
+        <v>0.2289135917295087</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1660201041381024</v>
+        <v>0.1622469199531456</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1788815230936944</v>
+        <v>0.1807815230936944</v>
       </c>
       <c r="C46">
-        <v>21.56442403871736</v>
+        <v>19.99002160210203</v>
       </c>
       <c r="D46">
-        <v>49.11362403871736</v>
+        <v>48.60852160210204</v>
       </c>
       <c r="E46">
-        <v>38.7192</v>
+        <v>39.7885</v>
       </c>
       <c r="F46">
-        <v>47.0492</v>
+        <v>48.1185</v>
       </c>
       <c r="G46">
         <v>19.5</v>
@@ -5059,37 +5059,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M46">
-        <v>11.09420136</v>
+        <v>11.3463423</v>
       </c>
       <c r="N46">
-        <v>-9.294201360000001</v>
+        <v>-9.546342300000001</v>
       </c>
       <c r="O46">
-        <v>-1.6729562448</v>
+        <v>-1.718341614</v>
       </c>
       <c r="P46">
-        <v>-7.621245115200001</v>
+        <v>-7.828000686000001</v>
       </c>
       <c r="Q46">
-        <v>2.7787548848</v>
+        <v>2.571999313999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1395706120226974</v>
+        <v>0.1412755322412919</v>
       </c>
       <c r="T46">
-        <v>1.581107231590188</v>
+        <v>1.609854635800919</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02920444559156621</v>
+        <v>0.02855545791175362</v>
       </c>
       <c r="W46">
-        <v>0.2289135917295087</v>
+        <v>0.2290666230244085</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1622469199531456</v>
+        <v>0.1586414328430756</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1807815230936944</v>
+        <v>0.1826815230936944</v>
       </c>
       <c r="C47">
-        <v>19.99002160210203</v>
+        <v>18.42590272129712</v>
       </c>
       <c r="D47">
-        <v>48.60852160210204</v>
+        <v>48.11370272129712</v>
       </c>
       <c r="E47">
-        <v>39.7885</v>
+        <v>40.8578</v>
       </c>
       <c r="F47">
-        <v>48.1185</v>
+        <v>49.1878</v>
       </c>
       <c r="G47">
         <v>19.5</v>
@@ -5141,37 +5141,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M47">
-        <v>11.3463423</v>
+        <v>11.59848324</v>
       </c>
       <c r="N47">
-        <v>-9.546342300000001</v>
+        <v>-9.798483240000001</v>
       </c>
       <c r="O47">
-        <v>-1.718341614</v>
+        <v>-1.7637269832</v>
       </c>
       <c r="P47">
-        <v>-7.828000686000001</v>
+        <v>-8.034756256800001</v>
       </c>
       <c r="Q47">
-        <v>2.571999313999999</v>
+        <v>2.365243743199999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1412755322412919</v>
+        <v>0.1430435976531676</v>
       </c>
       <c r="T47">
-        <v>1.609854635800919</v>
+        <v>1.639666758686121</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02855545791175362</v>
+        <v>0.02793468708758506</v>
       </c>
       <c r="W47">
-        <v>0.2290666230244085</v>
+        <v>0.2292130007847475</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1586414328430756</v>
+        <v>0.1551927060421393</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1826815230936944</v>
+        <v>0.1845815230936944</v>
       </c>
       <c r="C48">
-        <v>18.42590272129712</v>
+        <v>16.87175651128783</v>
       </c>
       <c r="D48">
-        <v>48.11370272129712</v>
+        <v>47.62885651128783</v>
       </c>
       <c r="E48">
-        <v>40.8578</v>
+        <v>41.9271</v>
       </c>
       <c r="F48">
-        <v>49.1878</v>
+        <v>50.2571</v>
       </c>
       <c r="G48">
         <v>19.5</v>
@@ -5223,37 +5223,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M48">
-        <v>11.59848324</v>
+        <v>11.85062418</v>
       </c>
       <c r="N48">
-        <v>-9.798483240000001</v>
+        <v>-10.05062418</v>
       </c>
       <c r="O48">
-        <v>-1.7637269832</v>
+        <v>-1.8091123524</v>
       </c>
       <c r="P48">
-        <v>-8.034756256800001</v>
+        <v>-8.241511827600002</v>
       </c>
       <c r="Q48">
-        <v>2.365243743199999</v>
+        <v>2.158488172399998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1430435976531676</v>
+        <v>0.1448783825145481</v>
       </c>
       <c r="T48">
-        <v>1.639666758686121</v>
+        <v>1.670603867340576</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02793468708758506</v>
+        <v>0.02734033204316836</v>
       </c>
       <c r="W48">
-        <v>0.2292130007847475</v>
+        <v>0.2293531497042209</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1551927060421393</v>
+        <v>0.1518907335731575</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1845815230936944</v>
+        <v>0.1864815230936944</v>
       </c>
       <c r="C49">
-        <v>16.87175651128783</v>
+        <v>15.32728449330812</v>
       </c>
       <c r="D49">
-        <v>47.62885651128783</v>
+        <v>47.15368449330812</v>
       </c>
       <c r="E49">
-        <v>41.9271</v>
+        <v>42.9964</v>
       </c>
       <c r="F49">
-        <v>50.2571</v>
+        <v>51.3264</v>
       </c>
       <c r="G49">
         <v>19.5</v>
@@ -5305,37 +5305,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M49">
-        <v>11.85062418</v>
+        <v>12.10276512</v>
       </c>
       <c r="N49">
-        <v>-10.05062418</v>
+        <v>-10.30276512</v>
       </c>
       <c r="O49">
-        <v>-1.8091123524</v>
+        <v>-1.8544977216</v>
       </c>
       <c r="P49">
-        <v>-8.241511827600002</v>
+        <v>-8.448267398400002</v>
       </c>
       <c r="Q49">
-        <v>2.158488172399998</v>
+        <v>1.951732601599998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1448783825145481</v>
+        <v>0.1467837360244433</v>
       </c>
       <c r="T49">
-        <v>1.670603867340576</v>
+        <v>1.702730864789433</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02734033204316836</v>
+        <v>0.02677074179226902</v>
       </c>
       <c r="W49">
-        <v>0.2293531497042209</v>
+        <v>0.229487459085383</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1518907335731575</v>
+        <v>0.1487263432903835</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1864815230936943</v>
+        <v>0.1883815230936943</v>
       </c>
       <c r="C50">
-        <v>15.32728449330814</v>
+        <v>13.7921999820955</v>
       </c>
       <c r="D50">
-        <v>47.15368449330813</v>
+        <v>46.68789998209549</v>
       </c>
       <c r="E50">
-        <v>42.99639999999999</v>
+        <v>44.0657</v>
       </c>
       <c r="F50">
-        <v>51.32639999999999</v>
+        <v>52.3957</v>
       </c>
       <c r="G50">
         <v>19.5</v>
@@ -5387,37 +5387,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M50">
-        <v>12.10276512</v>
+        <v>12.35490606</v>
       </c>
       <c r="N50">
-        <v>-10.30276512</v>
+        <v>-10.55490606</v>
       </c>
       <c r="O50">
-        <v>-1.8544977216</v>
+        <v>-1.8998830908</v>
       </c>
       <c r="P50">
-        <v>-8.448267398400001</v>
+        <v>-8.655022969200001</v>
       </c>
       <c r="Q50">
-        <v>1.9517326016</v>
+        <v>1.744977030799999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1467837360244433</v>
+        <v>0.1487638092798245</v>
       </c>
       <c r="T50">
-        <v>1.702730864789433</v>
+        <v>1.736117744491187</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02677074179226903</v>
+        <v>0.02622440012303904</v>
       </c>
       <c r="W50">
-        <v>0.229487459085383</v>
+        <v>0.2296162864509874</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1487263432903835</v>
+        <v>0.1456911117946613</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1883815230936943</v>
+        <v>0.1902815230936943</v>
       </c>
       <c r="C51">
-        <v>13.7921999820955</v>
+        <v>12.26622750910676</v>
       </c>
       <c r="D51">
-        <v>46.68789998209549</v>
+        <v>46.23122750910676</v>
       </c>
       <c r="E51">
-        <v>44.0657</v>
+        <v>45.135</v>
       </c>
       <c r="F51">
-        <v>52.3957</v>
+        <v>53.465</v>
       </c>
       <c r="G51">
         <v>19.5</v>
@@ -5469,37 +5469,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M51">
-        <v>12.35490606</v>
+        <v>12.607047</v>
       </c>
       <c r="N51">
-        <v>-10.55490606</v>
+        <v>-10.807047</v>
       </c>
       <c r="O51">
-        <v>-1.8998830908</v>
+        <v>-1.94526846</v>
       </c>
       <c r="P51">
-        <v>-8.655022969200001</v>
+        <v>-8.861778540000001</v>
       </c>
       <c r="Q51">
-        <v>1.744977030799999</v>
+        <v>1.538221459999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1487638092798245</v>
+        <v>0.150823085465421</v>
       </c>
       <c r="T51">
-        <v>1.736117744491187</v>
+        <v>1.770840099381011</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02622440012303904</v>
+        <v>0.02569991212057826</v>
       </c>
       <c r="W51">
-        <v>0.2296162864509874</v>
+        <v>0.2297399607219676</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1456911117946613</v>
+        <v>0.1427772895587681</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1902815230936943</v>
+        <v>0.1921815230936944</v>
       </c>
       <c r="C52">
-        <v>12.26622750910676</v>
+        <v>10.74910227925654</v>
       </c>
       <c r="D52">
-        <v>46.23122750910676</v>
+        <v>45.78340227925654</v>
       </c>
       <c r="E52">
-        <v>45.135</v>
+        <v>46.2043</v>
       </c>
       <c r="F52">
-        <v>53.465</v>
+        <v>54.53429999999999</v>
       </c>
       <c r="G52">
         <v>19.5</v>
@@ -5551,37 +5551,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M52">
-        <v>12.607047</v>
+        <v>12.85918794</v>
       </c>
       <c r="N52">
-        <v>-10.807047</v>
+        <v>-11.05918794</v>
       </c>
       <c r="O52">
-        <v>-1.94526846</v>
+        <v>-1.9906538292</v>
       </c>
       <c r="P52">
-        <v>-8.861778540000001</v>
+        <v>-9.068534110800002</v>
       </c>
       <c r="Q52">
-        <v>1.538221459999999</v>
+        <v>1.331465889199999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.150823085465421</v>
+        <v>0.1529664137402255</v>
       </c>
       <c r="T52">
-        <v>1.770840099381011</v>
+        <v>1.806979693245929</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02569991212057826</v>
+        <v>0.02519599227507673</v>
       </c>
       <c r="W52">
-        <v>0.2297399607219676</v>
+        <v>0.2298587850215369</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1427772895587681</v>
+        <v>0.1399777348615374</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1921815230936944</v>
+        <v>0.1940815230936944</v>
       </c>
       <c r="C53">
-        <v>10.74910227925654</v>
+        <v>9.240569658927001</v>
       </c>
       <c r="D53">
-        <v>45.78340227925654</v>
+        <v>45.34416965892699</v>
       </c>
       <c r="E53">
-        <v>46.2043</v>
+        <v>47.2736</v>
       </c>
       <c r="F53">
-        <v>54.53429999999999</v>
+        <v>55.6036</v>
       </c>
       <c r="G53">
         <v>19.5</v>
@@ -5633,37 +5633,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M53">
-        <v>12.85918794</v>
+        <v>13.11132888</v>
       </c>
       <c r="N53">
-        <v>-11.05918794</v>
+        <v>-11.31132888</v>
       </c>
       <c r="O53">
-        <v>-1.9906538292</v>
+        <v>-2.0360391984</v>
       </c>
       <c r="P53">
-        <v>-9.068534110800002</v>
+        <v>-9.2752896816</v>
       </c>
       <c r="Q53">
-        <v>1.331465889199999</v>
+        <v>1.1247103184</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1529664137402255</v>
+        <v>0.1551990473598136</v>
       </c>
       <c r="T53">
-        <v>1.806979693245929</v>
+        <v>1.844625103521886</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02519599227507673</v>
+        <v>0.02471145396209448</v>
       </c>
       <c r="W53">
-        <v>0.2298587850215369</v>
+        <v>0.2299730391557381</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1399777348615374</v>
+        <v>0.1372858553449693</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1940815230936944</v>
+        <v>0.1959815230936943</v>
       </c>
       <c r="C54">
-        <v>9.240569658927001</v>
+        <v>7.740384693168878</v>
       </c>
       <c r="D54">
-        <v>45.34416965892699</v>
+        <v>44.91328469316888</v>
       </c>
       <c r="E54">
-        <v>47.2736</v>
+        <v>48.3429</v>
       </c>
       <c r="F54">
-        <v>55.6036</v>
+        <v>56.6729</v>
       </c>
       <c r="G54">
         <v>19.5</v>
@@ -5715,37 +5715,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M54">
-        <v>13.11132888</v>
+        <v>13.36346982</v>
       </c>
       <c r="N54">
-        <v>-11.31132888</v>
+        <v>-11.56346982</v>
       </c>
       <c r="O54">
-        <v>-2.0360391984</v>
+        <v>-2.0814245676</v>
       </c>
       <c r="P54">
-        <v>-9.2752896816</v>
+        <v>-9.482045252400003</v>
       </c>
       <c r="Q54">
-        <v>1.1247103184</v>
+        <v>0.9179547475999978</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1551990473598136</v>
+        <v>0.1575266866653415</v>
       </c>
       <c r="T54">
-        <v>1.844625103521886</v>
+        <v>1.883872446150011</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02471145396209448</v>
+        <v>0.02424520011375307</v>
       </c>
       <c r="W54">
-        <v>0.2299730391557381</v>
+        <v>0.230082981813177</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1372858553449693</v>
+        <v>0.1346955561875171</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1959815230936943</v>
+        <v>0.1978815230936944</v>
       </c>
       <c r="C55">
-        <v>7.740384693168878</v>
+        <v>6.248311650170393</v>
       </c>
       <c r="D55">
-        <v>44.91328469316888</v>
+        <v>44.49051165017039</v>
       </c>
       <c r="E55">
-        <v>48.3429</v>
+        <v>49.4122</v>
       </c>
       <c r="F55">
-        <v>56.6729</v>
+        <v>57.7422</v>
       </c>
       <c r="G55">
         <v>19.5</v>
@@ -5797,37 +5797,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M55">
-        <v>13.36346982</v>
+        <v>13.61561076</v>
       </c>
       <c r="N55">
-        <v>-11.56346982</v>
+        <v>-11.81561076</v>
       </c>
       <c r="O55">
-        <v>-2.0814245676</v>
+        <v>-2.1268099368</v>
       </c>
       <c r="P55">
-        <v>-9.482045252400003</v>
+        <v>-9.688800823200001</v>
       </c>
       <c r="Q55">
-        <v>0.9179547475999978</v>
+        <v>0.7111991767999992</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1575266866653415</v>
+        <v>0.1599555276798055</v>
       </c>
       <c r="T55">
-        <v>1.883872446150011</v>
+        <v>1.924826194979359</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02424520011375307</v>
+        <v>0.02379621492646136</v>
       </c>
       <c r="W55">
-        <v>0.230082981813177</v>
+        <v>0.2301888525203404</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1346955561875171</v>
+        <v>0.1322011940358964</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1978815230936944</v>
+        <v>0.1997815230936943</v>
       </c>
       <c r="C56">
-        <v>6.248311650170393</v>
+        <v>4.764123591213789</v>
       </c>
       <c r="D56">
-        <v>44.49051165017039</v>
+        <v>44.07562359121379</v>
       </c>
       <c r="E56">
-        <v>49.4122</v>
+        <v>50.4815</v>
       </c>
       <c r="F56">
-        <v>57.7422</v>
+        <v>58.8115</v>
       </c>
       <c r="G56">
         <v>19.5</v>
@@ -5879,37 +5879,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M56">
-        <v>13.61561076</v>
+        <v>13.8677517</v>
       </c>
       <c r="N56">
-        <v>-11.81561076</v>
+        <v>-12.0677517</v>
       </c>
       <c r="O56">
-        <v>-2.1268099368</v>
+        <v>-2.172195306</v>
       </c>
       <c r="P56">
-        <v>-9.688800823200001</v>
+        <v>-9.895556394000002</v>
       </c>
       <c r="Q56">
-        <v>0.7111991767999992</v>
+        <v>0.5044436059999988</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1599555276798055</v>
+        <v>0.1624923171838012</v>
       </c>
       <c r="T56">
-        <v>1.924826194979359</v>
+        <v>1.967600110423345</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02379621492646136</v>
+        <v>0.02336355647325296</v>
       </c>
       <c r="W56">
-        <v>0.2301888525203404</v>
+        <v>0.230290873383607</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1322011940358964</v>
+        <v>0.1297975359625164</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1997815230936943</v>
+        <v>0.2016815230936944</v>
       </c>
       <c r="C57">
-        <v>4.764123591213789</v>
+        <v>3.287601964471563</v>
       </c>
       <c r="D57">
-        <v>44.07562359121379</v>
+        <v>43.66840196447156</v>
       </c>
       <c r="E57">
-        <v>50.4815</v>
+        <v>51.5508</v>
       </c>
       <c r="F57">
-        <v>58.8115</v>
+        <v>59.8808</v>
       </c>
       <c r="G57">
         <v>19.5</v>
@@ -5961,37 +5961,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M57">
-        <v>13.8677517</v>
+        <v>14.11989264</v>
       </c>
       <c r="N57">
-        <v>-12.0677517</v>
+        <v>-12.31989264</v>
       </c>
       <c r="O57">
-        <v>-2.172195306</v>
+        <v>-2.2175806752</v>
       </c>
       <c r="P57">
-        <v>-9.895556394000002</v>
+        <v>-10.1023119648</v>
       </c>
       <c r="Q57">
-        <v>0.5044436059999988</v>
+        <v>0.2976880351999984</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1624923171838012</v>
+        <v>0.1651444153016148</v>
       </c>
       <c r="T57">
-        <v>1.967600110423345</v>
+        <v>2.012318294751149</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02336355647325296</v>
+        <v>0.02294635010765916</v>
       </c>
       <c r="W57">
-        <v>0.230290873383607</v>
+        <v>0.230389250644614</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1297975359625164</v>
+        <v>0.1274797228203287</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2016815230936944</v>
+        <v>0.2035815230936943</v>
       </c>
       <c r="C58">
-        <v>3.287601964471563</v>
+        <v>1.818536221114243</v>
       </c>
       <c r="D58">
-        <v>43.66840196447156</v>
+        <v>43.26863622111424</v>
       </c>
       <c r="E58">
-        <v>51.5508</v>
+        <v>52.6201</v>
       </c>
       <c r="F58">
-        <v>59.8808</v>
+        <v>60.9501</v>
       </c>
       <c r="G58">
         <v>19.5</v>
@@ -6043,37 +6043,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M58">
-        <v>14.11989264</v>
+        <v>14.37203358</v>
       </c>
       <c r="N58">
-        <v>-12.31989264</v>
+        <v>-12.57203358</v>
       </c>
       <c r="O58">
-        <v>-2.2175806752</v>
+        <v>-2.2629660444</v>
       </c>
       <c r="P58">
-        <v>-10.1023119648</v>
+        <v>-10.3090675356</v>
       </c>
       <c r="Q58">
-        <v>0.2976880351999984</v>
+        <v>0.0909324643999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1651444153016148</v>
+        <v>0.167919866820257</v>
       </c>
       <c r="T58">
-        <v>2.012318294751149</v>
+        <v>2.059116394629082</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02294635010765916</v>
+        <v>0.02254378256191075</v>
       </c>
       <c r="W58">
-        <v>0.230389250644614</v>
+        <v>0.2304841760719014</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1274797228203287</v>
+        <v>0.1252432364550597</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2035815230936943</v>
+        <v>0.2054815230936943</v>
       </c>
       <c r="C59">
-        <v>1.818536221114243</v>
+        <v>0.3567234523131333</v>
       </c>
       <c r="D59">
-        <v>43.26863622111424</v>
+        <v>42.87612345231314</v>
       </c>
       <c r="E59">
-        <v>52.6201</v>
+        <v>53.68940000000001</v>
       </c>
       <c r="F59">
-        <v>60.9501</v>
+        <v>62.0194</v>
       </c>
       <c r="G59">
         <v>19.5</v>
@@ -6125,37 +6125,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M59">
-        <v>14.37203358</v>
+        <v>14.62417452</v>
       </c>
       <c r="N59">
-        <v>-12.57203358</v>
+        <v>-12.82417452</v>
       </c>
       <c r="O59">
-        <v>-2.2629660444</v>
+        <v>-2.308351413600001</v>
       </c>
       <c r="P59">
-        <v>-10.3090675356</v>
+        <v>-10.5158231064</v>
       </c>
       <c r="Q59">
-        <v>0.0909324643999998</v>
+        <v>-0.1158231064000024</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.167919866820257</v>
+        <v>0.1708274826969298</v>
       </c>
       <c r="T59">
-        <v>2.059116394629082</v>
+        <v>2.108142975453584</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02254378256191075</v>
+        <v>0.02215509665567091</v>
       </c>
       <c r="W59">
-        <v>0.2304841760719014</v>
+        <v>0.2305758282085928</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1252432364550597</v>
+        <v>0.1230838703092828</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2054815230936943</v>
+        <v>0.2073815230936943</v>
       </c>
       <c r="C60">
-        <v>0.3567234523131475</v>
+        <v>-1.098031954176797</v>
       </c>
       <c r="D60">
-        <v>42.87612345231314</v>
+        <v>42.4906680458232</v>
       </c>
       <c r="E60">
-        <v>53.68939999999999</v>
+        <v>54.7587</v>
       </c>
       <c r="F60">
-        <v>62.01939999999999</v>
+        <v>63.0887</v>
       </c>
       <c r="G60">
         <v>19.5</v>
@@ -6207,37 +6207,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M60">
-        <v>14.62417452</v>
+        <v>14.87631546</v>
       </c>
       <c r="N60">
-        <v>-12.82417452</v>
+        <v>-13.07631546</v>
       </c>
       <c r="O60">
-        <v>-2.3083514136</v>
+        <v>-2.3537367828</v>
       </c>
       <c r="P60">
-        <v>-10.5158231064</v>
+        <v>-10.7225786772</v>
       </c>
       <c r="Q60">
-        <v>-0.1158231063999988</v>
+        <v>-0.3225786771999992</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1708274826969298</v>
+        <v>0.1738769334944159</v>
       </c>
       <c r="T60">
-        <v>2.108142975453584</v>
+        <v>2.15956109680611</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02215509665567092</v>
+        <v>0.02177958654286294</v>
       </c>
       <c r="W60">
-        <v>0.2305758282085928</v>
+        <v>0.2306643734931929</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1230838703092829</v>
+        <v>0.1209977030159052</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2073815230936943</v>
+        <v>0.2092815230936944</v>
       </c>
       <c r="C61">
-        <v>-1.098031954176797</v>
+        <v>-2.545918639075353</v>
       </c>
       <c r="D61">
-        <v>42.4906680458232</v>
+        <v>42.11208136092463</v>
       </c>
       <c r="E61">
-        <v>54.7587</v>
+        <v>55.82799999999999</v>
       </c>
       <c r="F61">
-        <v>63.0887</v>
+        <v>64.15799999999999</v>
       </c>
       <c r="G61">
         <v>19.5</v>
@@ -6289,37 +6289,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M61">
-        <v>14.87631546</v>
+        <v>15.1284564</v>
       </c>
       <c r="N61">
-        <v>-13.07631546</v>
+        <v>-13.3284564</v>
       </c>
       <c r="O61">
-        <v>-2.3537367828</v>
+        <v>-2.399122151999999</v>
       </c>
       <c r="P61">
-        <v>-10.7225786772</v>
+        <v>-10.929334248</v>
       </c>
       <c r="Q61">
-        <v>-0.3225786771999992</v>
+        <v>-0.5293342479999996</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1738769334944159</v>
+        <v>0.1770788568317763</v>
       </c>
       <c r="T61">
-        <v>2.15956109680611</v>
+        <v>2.213550124226263</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02177958654286294</v>
+        <v>0.02141659343381522</v>
       </c>
       <c r="W61">
-        <v>0.2306643734931929</v>
+        <v>0.2307499672683064</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1209977030159052</v>
+        <v>0.1189810746323068</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2092815230936944</v>
+        <v>0.2111815230936944</v>
       </c>
       <c r="C62">
-        <v>-2.545918639075353</v>
+        <v>-3.987118579411522</v>
       </c>
       <c r="D62">
-        <v>42.11208136092463</v>
+        <v>41.74018142058848</v>
       </c>
       <c r="E62">
-        <v>55.82799999999999</v>
+        <v>56.8973</v>
       </c>
       <c r="F62">
-        <v>64.15799999999999</v>
+        <v>65.2273</v>
       </c>
       <c r="G62">
         <v>19.5</v>
@@ -6371,37 +6371,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M62">
-        <v>15.1284564</v>
+        <v>15.38059734</v>
       </c>
       <c r="N62">
-        <v>-13.3284564</v>
+        <v>-13.58059734</v>
       </c>
       <c r="O62">
-        <v>-2.399122151999999</v>
+        <v>-2.4445075212</v>
       </c>
       <c r="P62">
-        <v>-10.929334248</v>
+        <v>-11.1360898188</v>
       </c>
       <c r="Q62">
-        <v>-0.5293342479999996</v>
+        <v>-0.7360898188000018</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1770788568317763</v>
+        <v>0.1804449813659244</v>
       </c>
       <c r="T62">
-        <v>2.213550124226263</v>
+        <v>2.270307819719245</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02141659343381522</v>
+        <v>0.0210655017381789</v>
       </c>
       <c r="W62">
-        <v>0.2307499672683064</v>
+        <v>0.2308327546901374</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1189810746323068</v>
+        <v>0.117030565212105</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2111815230936944</v>
+        <v>0.2130815230936943</v>
       </c>
       <c r="C63">
-        <v>-3.987118579411522</v>
+        <v>-5.421807380189378</v>
       </c>
       <c r="D63">
-        <v>41.74018142058848</v>
+        <v>41.37479261981062</v>
       </c>
       <c r="E63">
-        <v>56.8973</v>
+        <v>57.9666</v>
       </c>
       <c r="F63">
-        <v>65.2273</v>
+        <v>66.2966</v>
       </c>
       <c r="G63">
         <v>19.5</v>
@@ -6453,37 +6453,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M63">
-        <v>15.38059734</v>
+        <v>15.63273828</v>
       </c>
       <c r="N63">
-        <v>-13.58059734</v>
+        <v>-13.83273828</v>
       </c>
       <c r="O63">
-        <v>-2.4445075212</v>
+        <v>-2.4898928904</v>
       </c>
       <c r="P63">
-        <v>-11.1360898188</v>
+        <v>-11.3428453896</v>
       </c>
       <c r="Q63">
-        <v>-0.7360898188000018</v>
+        <v>-0.9428453896000004</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1804449813659244</v>
+        <v>0.1839882703492382</v>
       </c>
       <c r="T63">
-        <v>2.270307819719245</v>
+        <v>2.330052762343435</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0210655017381789</v>
+        <v>0.0207257355811115</v>
       </c>
       <c r="W63">
-        <v>0.2308327546901374</v>
+        <v>0.2309128715499739</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.117030565212105</v>
+        <v>0.1151429754506195</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2130815230936943</v>
+        <v>0.2149815230936943</v>
       </c>
       <c r="C64">
-        <v>-5.421807380189378</v>
+        <v>-6.850154550867863</v>
       </c>
       <c r="D64">
-        <v>41.37479261981062</v>
+        <v>41.01574544913213</v>
       </c>
       <c r="E64">
-        <v>57.9666</v>
+        <v>59.0359</v>
       </c>
       <c r="F64">
-        <v>66.2966</v>
+        <v>67.3659</v>
       </c>
       <c r="G64">
         <v>19.5</v>
@@ -6535,37 +6535,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M64">
-        <v>15.63273828</v>
+        <v>15.88487922</v>
       </c>
       <c r="N64">
-        <v>-13.83273828</v>
+        <v>-14.08487922</v>
       </c>
       <c r="O64">
-        <v>-2.4898928904</v>
+        <v>-2.5352782596</v>
       </c>
       <c r="P64">
-        <v>-11.3428453896</v>
+        <v>-11.5496009604</v>
       </c>
       <c r="Q64">
-        <v>-0.9428453896000004</v>
+        <v>-1.149600960400001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1839882703492382</v>
+        <v>0.1877230884667852</v>
       </c>
       <c r="T64">
-        <v>2.330052762343435</v>
+        <v>2.39302716132569</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0207257355811115</v>
+        <v>0.02039675565125259</v>
       </c>
       <c r="W64">
-        <v>0.2309128715499739</v>
+        <v>0.2309904450174347</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1151429754506195</v>
+        <v>0.1133153091736255</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2149815230936943</v>
+        <v>0.2168815230936944</v>
       </c>
       <c r="C65">
-        <v>-6.850154550867863</v>
+        <v>-8.272323767568501</v>
       </c>
       <c r="D65">
-        <v>41.01574544913213</v>
+        <v>40.66287623243149</v>
       </c>
       <c r="E65">
-        <v>59.0359</v>
+        <v>60.1052</v>
       </c>
       <c r="F65">
-        <v>67.3659</v>
+        <v>68.43519999999999</v>
       </c>
       <c r="G65">
         <v>19.5</v>
@@ -6617,37 +6617,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M65">
-        <v>15.88487922</v>
+        <v>16.13702016</v>
       </c>
       <c r="N65">
-        <v>-14.08487922</v>
+        <v>-14.33702016</v>
       </c>
       <c r="O65">
-        <v>-2.5352782596</v>
+        <v>-2.5806636288</v>
       </c>
       <c r="P65">
-        <v>-11.5496009604</v>
+        <v>-11.7563565312</v>
       </c>
       <c r="Q65">
-        <v>-1.149600960400001</v>
+        <v>-1.356356531199999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1877230884667852</v>
+        <v>0.1916653964797514</v>
       </c>
       <c r="T65">
-        <v>2.39302716132569</v>
+        <v>2.459500138029181</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02039675565125259</v>
+        <v>0.02007805634420176</v>
       </c>
       <c r="W65">
-        <v>0.2309904450174347</v>
+        <v>0.2310655943140372</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1133153091736255</v>
+        <v>0.1115447574677876</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2168815230936944</v>
+        <v>0.2187815230936943</v>
       </c>
       <c r="C66">
-        <v>-8.272323767568501</v>
+        <v>-9.688473121863744</v>
       </c>
       <c r="D66">
-        <v>40.66287623243149</v>
+        <v>40.31602687813625</v>
       </c>
       <c r="E66">
-        <v>60.1052</v>
+        <v>61.17449999999999</v>
       </c>
       <c r="F66">
-        <v>68.43519999999999</v>
+        <v>69.50449999999999</v>
       </c>
       <c r="G66">
         <v>19.5</v>
@@ -6699,37 +6699,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M66">
-        <v>16.13702016</v>
+        <v>16.3891611</v>
       </c>
       <c r="N66">
-        <v>-14.33702016</v>
+        <v>-14.5891611</v>
       </c>
       <c r="O66">
-        <v>-2.5806636288</v>
+        <v>-2.626048998</v>
       </c>
       <c r="P66">
-        <v>-11.7563565312</v>
+        <v>-11.963112102</v>
       </c>
       <c r="Q66">
-        <v>-1.356356531199999</v>
+        <v>-1.563112102</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1916653964797514</v>
+        <v>0.1958329792363158</v>
       </c>
       <c r="T66">
-        <v>2.459500138029181</v>
+        <v>2.529771570544301</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02007805634420176</v>
+        <v>0.01976916316967559</v>
       </c>
       <c r="W66">
-        <v>0.2310655943140372</v>
+        <v>0.2311384313245905</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1115447574677876</v>
+        <v>0.1098286842759755</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2187815230936943</v>
+        <v>0.2206815230936944</v>
       </c>
       <c r="C67">
-        <v>-9.688473121863744</v>
+        <v>-11.09875535694013</v>
       </c>
       <c r="D67">
-        <v>40.31602687813625</v>
+        <v>39.97504464305986</v>
       </c>
       <c r="E67">
-        <v>61.17449999999999</v>
+        <v>62.24379999999999</v>
       </c>
       <c r="F67">
-        <v>69.50449999999999</v>
+        <v>70.57379999999999</v>
       </c>
       <c r="G67">
         <v>19.5</v>
@@ -6781,37 +6781,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M67">
-        <v>16.3891611</v>
+        <v>16.64130204</v>
       </c>
       <c r="N67">
-        <v>-14.5891611</v>
+        <v>-14.84130204</v>
       </c>
       <c r="O67">
-        <v>-2.626048998</v>
+        <v>-2.6714343672</v>
       </c>
       <c r="P67">
-        <v>-11.963112102</v>
+        <v>-12.1698676728</v>
       </c>
       <c r="Q67">
-        <v>-1.563112102</v>
+        <v>-1.7698676728</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1958329792363158</v>
+        <v>0.2002457139197368</v>
       </c>
       <c r="T67">
-        <v>2.529771570544301</v>
+        <v>2.604176616736781</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01976916316967559</v>
+        <v>0.01946963039437747</v>
       </c>
       <c r="W67">
-        <v>0.2311384313245905</v>
+        <v>0.2312090611530058</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1098286842759755</v>
+        <v>0.108164613302097</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2206815230936944</v>
+        <v>0.2225815230936943</v>
       </c>
       <c r="C68">
-        <v>-11.09875535694013</v>
+        <v>-12.5033180918775</v>
       </c>
       <c r="D68">
-        <v>39.97504464305986</v>
+        <v>39.63978190812251</v>
       </c>
       <c r="E68">
-        <v>62.24379999999999</v>
+        <v>63.31310000000001</v>
       </c>
       <c r="F68">
-        <v>70.57379999999999</v>
+        <v>71.6431</v>
       </c>
       <c r="G68">
         <v>19.5</v>
@@ -6863,37 +6863,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M68">
-        <v>16.64130204</v>
+        <v>16.89344298</v>
       </c>
       <c r="N68">
-        <v>-14.84130204</v>
+        <v>-15.09344298</v>
       </c>
       <c r="O68">
-        <v>-2.6714343672</v>
+        <v>-2.716819736400001</v>
       </c>
       <c r="P68">
-        <v>-12.1698676728</v>
+        <v>-12.3766232436</v>
       </c>
       <c r="Q68">
-        <v>-1.7698676728</v>
+        <v>-1.976623243600004</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2002457139197368</v>
+        <v>0.2049258870688198</v>
       </c>
       <c r="T68">
-        <v>2.604176616736781</v>
+        <v>2.683091059668198</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01946963039437747</v>
+        <v>0.01917903889595392</v>
       </c>
       <c r="W68">
-        <v>0.2312090611530058</v>
+        <v>0.2312775826283341</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.108164613302097</v>
+        <v>0.1065502160886329</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2225815230936943</v>
+        <v>0.2244815230936943</v>
       </c>
       <c r="C69">
-        <v>-12.5033180918775</v>
+        <v>-13.90230403473615</v>
       </c>
       <c r="D69">
-        <v>39.63978190812251</v>
+        <v>39.31009596526385</v>
       </c>
       <c r="E69">
-        <v>63.31310000000001</v>
+        <v>64.3824</v>
       </c>
       <c r="F69">
-        <v>71.6431</v>
+        <v>72.7124</v>
       </c>
       <c r="G69">
         <v>19.5</v>
@@ -6945,37 +6945,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M69">
-        <v>16.89344298</v>
+        <v>17.14558392</v>
       </c>
       <c r="N69">
-        <v>-15.09344298</v>
+        <v>-15.34558392</v>
       </c>
       <c r="O69">
-        <v>-2.716819736400001</v>
+        <v>-2.7622051056</v>
       </c>
       <c r="P69">
-        <v>-12.3766232436</v>
+        <v>-12.5833788144</v>
       </c>
       <c r="Q69">
-        <v>-1.976623243600004</v>
+        <v>-2.183378814400001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2049258870688198</v>
+        <v>0.2098985710397204</v>
       </c>
       <c r="T69">
-        <v>2.683091059668198</v>
+        <v>2.766937655282829</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01917903889595392</v>
+        <v>0.01889699420630754</v>
       </c>
       <c r="W69">
-        <v>0.2312775826283341</v>
+        <v>0.2313440887661527</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1065502160886329</v>
+        <v>0.1049833011461531</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2244815230936943</v>
+        <v>0.2263815230936944</v>
       </c>
       <c r="C70">
-        <v>-13.90230403473615</v>
+        <v>-15.29585118509832</v>
       </c>
       <c r="D70">
-        <v>39.31009596526385</v>
+        <v>38.98584881490168</v>
       </c>
       <c r="E70">
-        <v>64.3824</v>
+        <v>65.4517</v>
       </c>
       <c r="F70">
-        <v>72.7124</v>
+        <v>73.7817</v>
       </c>
       <c r="G70">
         <v>19.5</v>
@@ -7027,37 +7027,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M70">
-        <v>17.14558392</v>
+        <v>17.39772486</v>
       </c>
       <c r="N70">
-        <v>-15.34558392</v>
+        <v>-15.59772486</v>
       </c>
       <c r="O70">
-        <v>-2.7622051056</v>
+        <v>-2.8075904748</v>
       </c>
       <c r="P70">
-        <v>-12.5833788144</v>
+        <v>-12.7901343852</v>
       </c>
       <c r="Q70">
-        <v>-2.183378814400001</v>
+        <v>-2.390134385200001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2098985710397204</v>
+        <v>0.2151920733313243</v>
       </c>
       <c r="T70">
-        <v>2.766937655282829</v>
+        <v>2.85619370867905</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01889699420630754</v>
+        <v>0.01862312472505671</v>
       </c>
       <c r="W70">
-        <v>0.2313440887661527</v>
+        <v>0.2314086671898316</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1049833011461531</v>
+        <v>0.1034618040280928</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2263815230936944</v>
+        <v>0.2282815230936943</v>
       </c>
       <c r="C71">
-        <v>-15.29585118509832</v>
+        <v>-16.68409302666749</v>
       </c>
       <c r="D71">
-        <v>38.98584881490168</v>
+        <v>38.66690697333251</v>
       </c>
       <c r="E71">
-        <v>65.4517</v>
+        <v>66.521</v>
       </c>
       <c r="F71">
-        <v>73.7817</v>
+        <v>74.851</v>
       </c>
       <c r="G71">
         <v>19.5</v>
@@ -7109,37 +7109,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M71">
-        <v>17.39772486</v>
+        <v>17.6498658</v>
       </c>
       <c r="N71">
-        <v>-15.59772486</v>
+        <v>-15.8498658</v>
       </c>
       <c r="O71">
-        <v>-2.8075904748</v>
+        <v>-2.852975844</v>
       </c>
       <c r="P71">
-        <v>-12.7901343852</v>
+        <v>-12.996889956</v>
       </c>
       <c r="Q71">
-        <v>-2.390134385200001</v>
+        <v>-2.596889956</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2151920733313243</v>
+        <v>0.2208384757757017</v>
       </c>
       <c r="T71">
-        <v>2.85619370867905</v>
+        <v>2.951400165635018</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01862312472505671</v>
+        <v>0.01835708008612733</v>
       </c>
       <c r="W71">
-        <v>0.2314086671898316</v>
+        <v>0.2314714005156912</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1034618040280928</v>
+        <v>0.1019837782562629</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2282815230936943</v>
+        <v>0.2301815230936944</v>
       </c>
       <c r="C72">
-        <v>-16.68409302666749</v>
+        <v>-18.06715871049077</v>
       </c>
       <c r="D72">
-        <v>38.66690697333251</v>
+        <v>38.35314128950922</v>
       </c>
       <c r="E72">
-        <v>66.521</v>
+        <v>67.5903</v>
       </c>
       <c r="F72">
-        <v>74.851</v>
+        <v>75.9203</v>
       </c>
       <c r="G72">
         <v>19.5</v>
@@ -7191,37 +7191,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M72">
-        <v>17.6498658</v>
+        <v>17.90200674</v>
       </c>
       <c r="N72">
-        <v>-15.8498658</v>
+        <v>-16.10200674</v>
       </c>
       <c r="O72">
-        <v>-2.852975844</v>
+        <v>-2.8983612132</v>
       </c>
       <c r="P72">
-        <v>-12.996889956</v>
+        <v>-13.2036455268</v>
       </c>
       <c r="Q72">
-        <v>-2.596889956</v>
+        <v>-2.8036455268</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2208384757757017</v>
+        <v>0.2268742852852087</v>
       </c>
       <c r="T72">
-        <v>2.951400165635018</v>
+        <v>3.053172585139674</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01835708008612733</v>
+        <v>0.01809852966237906</v>
       </c>
       <c r="W72">
-        <v>0.2314714005156912</v>
+        <v>0.231532366705611</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1019837782562629</v>
+        <v>0.1005473870132171</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2301815230936943</v>
+        <v>0.2320815230936943</v>
       </c>
       <c r="C73">
-        <v>-18.06715871049075</v>
+        <v>-19.4451732293323</v>
       </c>
       <c r="D73">
-        <v>38.35314128950925</v>
+        <v>38.0444267706677</v>
       </c>
       <c r="E73">
-        <v>67.5903</v>
+        <v>68.6596</v>
       </c>
       <c r="F73">
-        <v>75.9203</v>
+        <v>76.9896</v>
       </c>
       <c r="G73">
         <v>19.5</v>
@@ -7273,37 +7273,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M73">
-        <v>17.90200674</v>
+        <v>18.15414768</v>
       </c>
       <c r="N73">
-        <v>-16.10200674</v>
+        <v>-16.35414768</v>
       </c>
       <c r="O73">
-        <v>-2.8983612132</v>
+        <v>-2.943746582400001</v>
       </c>
       <c r="P73">
-        <v>-13.2036455268</v>
+        <v>-13.4104010976</v>
       </c>
       <c r="Q73">
-        <v>-2.8036455268</v>
+        <v>-3.010401097600003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2268742852852087</v>
+        <v>0.2333412240453947</v>
       </c>
       <c r="T73">
-        <v>3.053172585139673</v>
+        <v>3.162214463180376</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01809852966237906</v>
+        <v>0.01784716119484601</v>
       </c>
       <c r="W73">
-        <v>0.231532366705611</v>
+        <v>0.2315916393902553</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1005473870132171</v>
+        <v>0.09915089552692224</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2320815230936943</v>
+        <v>0.2339815230936943</v>
       </c>
       <c r="C74">
-        <v>-19.4451732293323</v>
+        <v>-20.81825758369255</v>
       </c>
       <c r="D74">
-        <v>38.0444267706677</v>
+        <v>37.74064241630744</v>
       </c>
       <c r="E74">
-        <v>68.6596</v>
+        <v>69.7289</v>
       </c>
       <c r="F74">
-        <v>76.9896</v>
+        <v>78.05889999999999</v>
       </c>
       <c r="G74">
         <v>19.5</v>
@@ -7355,37 +7355,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M74">
-        <v>18.15414768</v>
+        <v>18.40628862</v>
       </c>
       <c r="N74">
-        <v>-16.35414768</v>
+        <v>-16.60628862</v>
       </c>
       <c r="O74">
-        <v>-2.943746582400001</v>
+        <v>-2.9891319516</v>
       </c>
       <c r="P74">
-        <v>-13.4104010976</v>
+        <v>-13.6171566684</v>
       </c>
       <c r="Q74">
-        <v>-3.010401097600003</v>
+        <v>-3.217156668399999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2333412240453947</v>
+        <v>0.2402871953063352</v>
       </c>
       <c r="T74">
-        <v>3.162214463180376</v>
+        <v>3.279333517372241</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01784716119484601</v>
+        <v>0.01760267953464265</v>
       </c>
       <c r="W74">
-        <v>0.2315916393902553</v>
+        <v>0.2316492881657313</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.09915089552692224</v>
+        <v>0.0977926640813479</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2339815230936943</v>
+        <v>0.2358815230936943</v>
       </c>
       <c r="C75">
-        <v>-20.81825758369255</v>
+        <v>-22.18652893993649</v>
       </c>
       <c r="D75">
-        <v>37.74064241630744</v>
+        <v>37.4416710600635</v>
       </c>
       <c r="E75">
-        <v>69.7289</v>
+        <v>70.79819999999999</v>
       </c>
       <c r="F75">
-        <v>78.05889999999999</v>
+        <v>79.12819999999999</v>
       </c>
       <c r="G75">
         <v>19.5</v>
@@ -7437,37 +7437,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M75">
-        <v>18.40628862</v>
+        <v>18.65842956</v>
       </c>
       <c r="N75">
-        <v>-16.60628862</v>
+        <v>-16.85842956</v>
       </c>
       <c r="O75">
-        <v>-2.9891319516</v>
+        <v>-3.0345173208</v>
       </c>
       <c r="P75">
-        <v>-13.6171566684</v>
+        <v>-13.8239122392</v>
       </c>
       <c r="Q75">
-        <v>-3.217156668399999</v>
+        <v>-3.423912239199998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2402871953063352</v>
+        <v>0.2477674720488866</v>
       </c>
       <c r="T75">
-        <v>3.279333517372241</v>
+        <v>3.405461729578866</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01760267953464265</v>
+        <v>0.01736480548687721</v>
       </c>
       <c r="W75">
-        <v>0.2316492881657313</v>
+        <v>0.2317053788661944</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0977926640813479</v>
+        <v>0.09647114159376236</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2358815230936943</v>
+        <v>0.2377815230936944</v>
       </c>
       <c r="C76">
-        <v>-22.18652893993649</v>
+        <v>-23.55010078096516</v>
       </c>
       <c r="D76">
-        <v>37.4416710600635</v>
+        <v>37.14739921903483</v>
       </c>
       <c r="E76">
-        <v>70.79819999999999</v>
+        <v>71.86749999999999</v>
       </c>
       <c r="F76">
-        <v>79.12819999999999</v>
+        <v>80.19749999999999</v>
       </c>
       <c r="G76">
         <v>19.5</v>
@@ -7519,37 +7519,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M76">
-        <v>18.65842956</v>
+        <v>18.9105705</v>
       </c>
       <c r="N76">
-        <v>-16.85842956</v>
+        <v>-17.1105705</v>
       </c>
       <c r="O76">
-        <v>-3.0345173208</v>
+        <v>-3.07990269</v>
       </c>
       <c r="P76">
-        <v>-13.8239122392</v>
+        <v>-14.03066781</v>
       </c>
       <c r="Q76">
-        <v>-3.423912239199998</v>
+        <v>-3.63066781</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2477674720488866</v>
+        <v>0.2558461709308421</v>
       </c>
       <c r="T76">
-        <v>3.405461729578866</v>
+        <v>3.541680198762021</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01736480548687721</v>
+        <v>0.01713327474705217</v>
       </c>
       <c r="W76">
-        <v>0.2317053788661944</v>
+        <v>0.2317599738146451</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09647114159376236</v>
+        <v>0.09518485970584534</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2377815230936944</v>
+        <v>0.2396815230936943</v>
       </c>
       <c r="C77">
-        <v>-23.55010078096516</v>
+        <v>-24.9090830498371</v>
       </c>
       <c r="D77">
-        <v>37.14739921903483</v>
+        <v>36.85771695016289</v>
       </c>
       <c r="E77">
-        <v>71.86749999999999</v>
+        <v>72.93679999999999</v>
       </c>
       <c r="F77">
-        <v>80.19749999999999</v>
+        <v>81.26679999999999</v>
       </c>
       <c r="G77">
         <v>19.5</v>
@@ -7601,37 +7601,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M77">
-        <v>18.9105705</v>
+        <v>19.16271144</v>
       </c>
       <c r="N77">
-        <v>-17.1105705</v>
+        <v>-17.36271144</v>
       </c>
       <c r="O77">
-        <v>-3.07990269</v>
+        <v>-3.125288059199999</v>
       </c>
       <c r="P77">
-        <v>-14.03066781</v>
+        <v>-14.2374233808</v>
       </c>
       <c r="Q77">
-        <v>-3.63066781</v>
+        <v>-3.837423380799999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2558461709308421</v>
+        <v>0.2645980947196271</v>
       </c>
       <c r="T77">
-        <v>3.541680198762021</v>
+        <v>3.689250207043772</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01713327474705217</v>
+        <v>0.01690783692143307</v>
       </c>
       <c r="W77">
-        <v>0.2317599738146451</v>
+        <v>0.2318131320539261</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.09518485970584534</v>
+        <v>0.09393242734129492</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2396815230936943</v>
+        <v>0.2415815230936944</v>
       </c>
       <c r="C78">
-        <v>-24.9090830498371</v>
+        <v>-26.26358228672242</v>
       </c>
       <c r="D78">
-        <v>36.85771695016289</v>
+        <v>36.57251771327758</v>
       </c>
       <c r="E78">
-        <v>72.93679999999999</v>
+        <v>74.0061</v>
       </c>
       <c r="F78">
-        <v>81.26679999999999</v>
+        <v>82.3361</v>
       </c>
       <c r="G78">
         <v>19.5</v>
@@ -7683,37 +7683,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M78">
-        <v>19.16271144</v>
+        <v>19.41485238</v>
       </c>
       <c r="N78">
-        <v>-17.36271144</v>
+        <v>-17.61485238</v>
       </c>
       <c r="O78">
-        <v>-3.125288059199999</v>
+        <v>-3.1706734284</v>
       </c>
       <c r="P78">
-        <v>-14.2374233808</v>
+        <v>-14.4441789516</v>
       </c>
       <c r="Q78">
-        <v>-3.837423380799999</v>
+        <v>-4.044178951600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2645980947196271</v>
+        <v>0.2741110553596109</v>
       </c>
       <c r="T78">
-        <v>3.689250207043772</v>
+        <v>3.849652389958718</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01690783692143307</v>
+        <v>0.01668825462375211</v>
       </c>
       <c r="W78">
-        <v>0.2318131320539261</v>
+        <v>0.2318649095597193</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.09393242734129492</v>
+        <v>0.09271252568751187</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2415815230936944</v>
+        <v>0.2434815230936944</v>
       </c>
       <c r="C79">
-        <v>-26.26358228672242</v>
+        <v>-27.61370175954664</v>
       </c>
       <c r="D79">
-        <v>36.57251771327758</v>
+        <v>36.29169824045336</v>
       </c>
       <c r="E79">
-        <v>74.0061</v>
+        <v>75.0754</v>
       </c>
       <c r="F79">
-        <v>82.3361</v>
+        <v>83.4054</v>
       </c>
       <c r="G79">
         <v>19.5</v>
@@ -7765,37 +7765,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M79">
-        <v>19.41485238</v>
+        <v>19.66699332</v>
       </c>
       <c r="N79">
-        <v>-17.61485238</v>
+        <v>-17.86699332</v>
       </c>
       <c r="O79">
-        <v>-3.1706734284</v>
+        <v>-3.2160587976</v>
       </c>
       <c r="P79">
-        <v>-14.4441789516</v>
+        <v>-14.6509345224</v>
       </c>
       <c r="Q79">
-        <v>-4.044178951600001</v>
+        <v>-4.2509345224</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2741110553596109</v>
+        <v>0.2844888306032297</v>
       </c>
       <c r="T79">
-        <v>3.849652389958718</v>
+        <v>4.024636589502298</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01668825462375211</v>
+        <v>0.01647430264139632</v>
       </c>
       <c r="W79">
-        <v>0.2318649095597193</v>
+        <v>0.2319153594371588</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.09271252568751187</v>
+        <v>0.09152390356331297</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2434815230936944</v>
+        <v>0.2453815230936944</v>
       </c>
       <c r="C80">
-        <v>-27.61370175954664</v>
+        <v>-28.95954158866212</v>
       </c>
       <c r="D80">
-        <v>36.29169824045336</v>
+        <v>36.01515841133788</v>
       </c>
       <c r="E80">
-        <v>75.0754</v>
+        <v>76.1447</v>
       </c>
       <c r="F80">
-        <v>83.4054</v>
+        <v>84.4747</v>
       </c>
       <c r="G80">
         <v>19.5</v>
@@ -7847,37 +7847,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M80">
-        <v>19.66699332</v>
+        <v>19.91913426</v>
       </c>
       <c r="N80">
-        <v>-17.86699332</v>
+        <v>-18.11913426</v>
       </c>
       <c r="O80">
-        <v>-3.2160587976</v>
+        <v>-3.2614441668</v>
       </c>
       <c r="P80">
-        <v>-14.6509345224</v>
+        <v>-14.8576900932</v>
       </c>
       <c r="Q80">
-        <v>-4.2509345224</v>
+        <v>-4.457690093200002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2844888306032297</v>
+        <v>0.2958549653938597</v>
       </c>
       <c r="T80">
-        <v>4.024636589502298</v>
+        <v>4.216285950907169</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01647430264139632</v>
+        <v>0.01626576716492295</v>
       </c>
       <c r="W80">
-        <v>0.2319153594371588</v>
+        <v>0.2319645321025112</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.09152390356331297</v>
+        <v>0.09036537313846071</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2453815230936944</v>
+        <v>0.2472815230936944</v>
       </c>
       <c r="C81">
-        <v>-28.95954158866212</v>
+        <v>-30.30119886586237</v>
       </c>
       <c r="D81">
-        <v>36.01515841133788</v>
+        <v>35.74280113413762</v>
       </c>
       <c r="E81">
-        <v>76.1447</v>
+        <v>77.214</v>
       </c>
       <c r="F81">
-        <v>84.4747</v>
+        <v>85.544</v>
       </c>
       <c r="G81">
         <v>19.5</v>
@@ -7929,37 +7929,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M81">
-        <v>19.91913426</v>
+        <v>20.1712752</v>
       </c>
       <c r="N81">
-        <v>-18.11913426</v>
+        <v>-18.3712752</v>
       </c>
       <c r="O81">
-        <v>-3.2614441668</v>
+        <v>-3.306829536</v>
       </c>
       <c r="P81">
-        <v>-14.8576900932</v>
+        <v>-15.064445664</v>
       </c>
       <c r="Q81">
-        <v>-4.457690093200002</v>
+        <v>-4.664445663999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2958549653938597</v>
+        <v>0.3083577136635526</v>
       </c>
       <c r="T81">
-        <v>4.216285950907169</v>
+        <v>4.427100248452527</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01626576716492295</v>
+        <v>0.01606244507536141</v>
       </c>
       <c r="W81">
-        <v>0.2319645321025112</v>
+        <v>0.2320124754512298</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.09036537313846071</v>
+        <v>0.0892358059742302</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2472815230936944</v>
+        <v>0.2491815230936944</v>
       </c>
       <c r="C82">
-        <v>-30.30119886586237</v>
+        <v>-31.63876776803687</v>
       </c>
       <c r="D82">
-        <v>35.74280113413762</v>
+        <v>35.47453223196312</v>
       </c>
       <c r="E82">
-        <v>77.214</v>
+        <v>78.2833</v>
       </c>
       <c r="F82">
-        <v>85.544</v>
+        <v>86.6133</v>
       </c>
       <c r="G82">
         <v>19.5</v>
@@ -8011,37 +8011,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M82">
-        <v>20.1712752</v>
+        <v>20.42341614</v>
       </c>
       <c r="N82">
-        <v>-18.3712752</v>
+        <v>-18.62341614</v>
       </c>
       <c r="O82">
-        <v>-3.306829536</v>
+        <v>-3.3522149052</v>
       </c>
       <c r="P82">
-        <v>-15.064445664</v>
+        <v>-15.2712012348</v>
       </c>
       <c r="Q82">
-        <v>-4.664445663999999</v>
+        <v>-4.871201234800003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3083577136635526</v>
+        <v>0.3221765406984765</v>
       </c>
       <c r="T82">
-        <v>4.427100248452527</v>
+        <v>4.660105524686871</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01606244507536141</v>
+        <v>0.01586414328430757</v>
       </c>
       <c r="W82">
-        <v>0.2320124754512298</v>
+        <v>0.2320592350135603</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.0892358059742302</v>
+        <v>0.08813412935726417</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2491815230936944</v>
+        <v>0.2510815230936944</v>
       </c>
       <c r="C83">
-        <v>-31.63876776803687</v>
+        <v>-32.9723396657457</v>
       </c>
       <c r="D83">
-        <v>35.47453223196312</v>
+        <v>35.21026033425429</v>
       </c>
       <c r="E83">
-        <v>78.2833</v>
+        <v>79.3526</v>
       </c>
       <c r="F83">
-        <v>86.6133</v>
+        <v>87.68259999999999</v>
       </c>
       <c r="G83">
         <v>19.5</v>
@@ -8093,37 +8093,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M83">
-        <v>20.42341614</v>
+        <v>20.67555708</v>
       </c>
       <c r="N83">
-        <v>-18.62341614</v>
+        <v>-18.87555708</v>
       </c>
       <c r="O83">
-        <v>-3.3522149052</v>
+        <v>-3.3976002744</v>
       </c>
       <c r="P83">
-        <v>-15.2712012348</v>
+        <v>-15.4779568056</v>
       </c>
       <c r="Q83">
-        <v>-4.871201234800003</v>
+        <v>-5.0779568056</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3221765406984765</v>
+        <v>0.3375307929595029</v>
       </c>
       <c r="T83">
-        <v>4.660105524686871</v>
+        <v>4.919000276058363</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01586414328430757</v>
+        <v>0.01567067812230382</v>
       </c>
       <c r="W83">
-        <v>0.2320592350135603</v>
+        <v>0.2321048540987608</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.08813412935726417</v>
+        <v>0.08705932290168794</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2510815230936944</v>
+        <v>0.2529815230936943</v>
       </c>
       <c r="C84">
-        <v>-32.9723396657457</v>
+        <v>-34.30200322697719</v>
       </c>
       <c r="D84">
-        <v>35.21026033425429</v>
+        <v>34.94989677302281</v>
       </c>
       <c r="E84">
-        <v>79.3526</v>
+        <v>80.42190000000001</v>
       </c>
       <c r="F84">
-        <v>87.68259999999999</v>
+        <v>88.75190000000001</v>
       </c>
       <c r="G84">
         <v>19.5</v>
@@ -8175,37 +8175,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M84">
-        <v>20.67555708</v>
+        <v>20.92769802</v>
       </c>
       <c r="N84">
-        <v>-18.87555708</v>
+        <v>-19.12769802</v>
       </c>
       <c r="O84">
-        <v>-3.3976002744</v>
+        <v>-3.442985643600001</v>
       </c>
       <c r="P84">
-        <v>-15.4779568056</v>
+        <v>-15.6847123764</v>
       </c>
       <c r="Q84">
-        <v>-5.0779568056</v>
+        <v>-5.284712376400003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3375307929595029</v>
+        <v>0.3546914278394737</v>
       </c>
       <c r="T84">
-        <v>4.919000276058363</v>
+        <v>5.208353233473562</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01567067812230382</v>
+        <v>0.01548187477143268</v>
       </c>
       <c r="W84">
-        <v>0.2321048540987608</v>
+        <v>0.2321493739288962</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08705932290168794</v>
+        <v>0.08601041539684817</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2529815230936943</v>
+        <v>0.2548815230936944</v>
       </c>
       <c r="C85">
-        <v>-34.30200322697719</v>
+        <v>-35.62784451633566</v>
       </c>
       <c r="D85">
-        <v>34.94989677302281</v>
+        <v>34.69335548366434</v>
       </c>
       <c r="E85">
-        <v>80.42190000000001</v>
+        <v>81.49120000000001</v>
       </c>
       <c r="F85">
-        <v>88.75190000000001</v>
+        <v>89.8212</v>
       </c>
       <c r="G85">
         <v>19.5</v>
@@ -8257,37 +8257,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M85">
-        <v>20.92769802</v>
+        <v>21.17983896</v>
       </c>
       <c r="N85">
-        <v>-19.12769802</v>
+        <v>-19.37983896</v>
       </c>
       <c r="O85">
-        <v>-3.442985643600001</v>
+        <v>-3.4883710128</v>
       </c>
       <c r="P85">
-        <v>-15.6847123764</v>
+        <v>-15.8914679472</v>
       </c>
       <c r="Q85">
-        <v>-5.284712376400003</v>
+        <v>-5.4914679472</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3546914278394737</v>
+        <v>0.373997142079441</v>
       </c>
       <c r="T85">
-        <v>5.208353233473562</v>
+        <v>5.533875310565661</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01548187477143268</v>
+        <v>0.01529756673843944</v>
       </c>
       <c r="W85">
-        <v>0.2321493739288962</v>
+        <v>0.232192833763076</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08601041539684817</v>
+        <v>0.08498648188021918</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2548815230936943</v>
+        <v>0.2567815230936943</v>
       </c>
       <c r="C86">
-        <v>-35.62784451633564</v>
+        <v>-36.9499470898928</v>
       </c>
       <c r="D86">
-        <v>34.69335548366435</v>
+        <v>34.44055291010719</v>
       </c>
       <c r="E86">
-        <v>81.49119999999999</v>
+        <v>82.56049999999999</v>
       </c>
       <c r="F86">
-        <v>89.82119999999999</v>
+        <v>90.89049999999999</v>
       </c>
       <c r="G86">
         <v>19.5</v>
@@ -8339,37 +8339,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M86">
-        <v>21.17983896</v>
+        <v>21.4319799</v>
       </c>
       <c r="N86">
-        <v>-19.37983896</v>
+        <v>-19.6319799</v>
       </c>
       <c r="O86">
-        <v>-3.4883710128</v>
+        <v>-3.533756382</v>
       </c>
       <c r="P86">
-        <v>-15.8914679472</v>
+        <v>-16.098223518</v>
       </c>
       <c r="Q86">
-        <v>-5.4914679472</v>
+        <v>-5.698223517999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3739971420794407</v>
+        <v>0.3958769515514034</v>
       </c>
       <c r="T86">
-        <v>5.533875310565657</v>
+        <v>5.902800331270035</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01529756673843944</v>
+        <v>0.01511759536504604</v>
       </c>
       <c r="W86">
-        <v>0.232192833763076</v>
+        <v>0.2322352710129221</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08498648188021907</v>
+        <v>0.08398664091692254</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2567815230936943</v>
+        <v>0.2586815230936944</v>
       </c>
       <c r="C87">
-        <v>-36.9499470898928</v>
+        <v>-38.26839208592212</v>
       </c>
       <c r="D87">
-        <v>34.44055291010719</v>
+        <v>34.19140791407786</v>
       </c>
       <c r="E87">
-        <v>82.56049999999999</v>
+        <v>83.62979999999999</v>
       </c>
       <c r="F87">
-        <v>90.89049999999999</v>
+        <v>91.95979999999999</v>
       </c>
       <c r="G87">
         <v>19.5</v>
@@ -8421,37 +8421,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M87">
-        <v>21.4319799</v>
+        <v>21.68412084</v>
       </c>
       <c r="N87">
-        <v>-19.6319799</v>
+        <v>-19.88412084</v>
       </c>
       <c r="O87">
-        <v>-3.533756382</v>
+        <v>-3.5791417512</v>
       </c>
       <c r="P87">
-        <v>-16.098223518</v>
+        <v>-16.3049790888</v>
       </c>
       <c r="Q87">
-        <v>-5.698223517999997</v>
+        <v>-5.904979088799999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3958769515514034</v>
+        <v>0.4208824480907894</v>
       </c>
       <c r="T87">
-        <v>5.902800331270035</v>
+        <v>6.324428926360752</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01511759536504604</v>
+        <v>0.01494180937242922</v>
       </c>
       <c r="W87">
-        <v>0.2322352710129221</v>
+        <v>0.2322767213499812</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08398664091692254</v>
+        <v>0.08301005206905121</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2586815230936944</v>
+        <v>0.2605815230936943</v>
       </c>
       <c r="C88">
-        <v>-38.26839208592212</v>
+        <v>-39.58325831172322</v>
       </c>
       <c r="D88">
-        <v>34.19140791407786</v>
+        <v>33.94584168827678</v>
       </c>
       <c r="E88">
-        <v>83.62979999999999</v>
+        <v>84.6991</v>
       </c>
       <c r="F88">
-        <v>91.95979999999999</v>
+        <v>93.0291</v>
       </c>
       <c r="G88">
         <v>19.5</v>
@@ -8503,37 +8503,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M88">
-        <v>21.68412084</v>
+        <v>21.93626178</v>
       </c>
       <c r="N88">
-        <v>-19.88412084</v>
+        <v>-20.13626178000001</v>
       </c>
       <c r="O88">
-        <v>-3.5791417512</v>
+        <v>-3.624527120400001</v>
       </c>
       <c r="P88">
-        <v>-16.3049790888</v>
+        <v>-16.51173465960001</v>
       </c>
       <c r="Q88">
-        <v>-5.904979088799999</v>
+        <v>-6.111734659600005</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4208824480907894</v>
+        <v>0.4497349440977731</v>
       </c>
       <c r="T88">
-        <v>6.324428926360752</v>
+        <v>6.810923459157732</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01494180937242922</v>
+        <v>0.01477006443711394</v>
       </c>
       <c r="W88">
-        <v>0.2322767213499812</v>
+        <v>0.2323172188057285</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08301005206905121</v>
+        <v>0.0820559135395218</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2605815230936943</v>
+        <v>0.2624815230936943</v>
       </c>
       <c r="C89">
-        <v>-39.58325831172322</v>
+        <v>-40.89462232673138</v>
       </c>
       <c r="D89">
-        <v>33.94584168827678</v>
+        <v>33.70377767326862</v>
       </c>
       <c r="E89">
-        <v>84.6991</v>
+        <v>85.7684</v>
       </c>
       <c r="F89">
-        <v>93.0291</v>
+        <v>94.0984</v>
       </c>
       <c r="G89">
         <v>19.5</v>
@@ -8585,37 +8585,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M89">
-        <v>21.93626178</v>
+        <v>22.18840272</v>
       </c>
       <c r="N89">
-        <v>-20.13626178000001</v>
+        <v>-20.38840272</v>
       </c>
       <c r="O89">
-        <v>-3.624527120400001</v>
+        <v>-3.6699124896</v>
       </c>
       <c r="P89">
-        <v>-16.51173465960001</v>
+        <v>-16.7184902304</v>
       </c>
       <c r="Q89">
-        <v>-6.111734659600005</v>
+        <v>-6.3184902304</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4497349440977731</v>
+        <v>0.4833961894392543</v>
       </c>
       <c r="T89">
-        <v>6.810923459157732</v>
+        <v>7.378500414087545</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01477006443711394</v>
+        <v>0.0146022227957831</v>
       </c>
       <c r="W89">
-        <v>0.2323172188057285</v>
+        <v>0.2323567958647543</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.0820559135395218</v>
+        <v>0.08112345997657266</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2624815230936943</v>
+        <v>0.2643815230936943</v>
       </c>
       <c r="C90">
-        <v>-40.89462232673138</v>
+        <v>-42.20255852209652</v>
       </c>
       <c r="D90">
-        <v>33.70377767326862</v>
+        <v>33.46514147790348</v>
       </c>
       <c r="E90">
-        <v>85.7684</v>
+        <v>86.8377</v>
       </c>
       <c r="F90">
-        <v>94.0984</v>
+        <v>95.1677</v>
       </c>
       <c r="G90">
         <v>19.5</v>
@@ -8667,37 +8667,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M90">
-        <v>22.18840272</v>
+        <v>22.44054366</v>
       </c>
       <c r="N90">
-        <v>-20.38840272</v>
+        <v>-20.64054366</v>
       </c>
       <c r="O90">
-        <v>-3.6699124896</v>
+        <v>-3.7152978588</v>
       </c>
       <c r="P90">
-        <v>-16.7184902304</v>
+        <v>-16.9252458012</v>
       </c>
       <c r="Q90">
-        <v>-6.3184902304</v>
+        <v>-6.525245801199999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4833961894392543</v>
+        <v>0.5231776612064594</v>
       </c>
       <c r="T90">
-        <v>7.378500414087545</v>
+        <v>8.049273179004595</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0146022227957831</v>
+        <v>0.01443815287672936</v>
       </c>
       <c r="W90">
-        <v>0.2323567958647543</v>
+        <v>0.2323954835516672</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08112345997657266</v>
+        <v>0.08021196042627432</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2643815230936943</v>
+        <v>0.2662815230936944</v>
       </c>
       <c r="C91">
-        <v>-42.20255852209652</v>
+        <v>-43.50713919690506</v>
       </c>
       <c r="D91">
-        <v>33.46514147790348</v>
+        <v>33.22986080309494</v>
       </c>
       <c r="E91">
-        <v>86.8377</v>
+        <v>87.907</v>
       </c>
       <c r="F91">
-        <v>95.1677</v>
+        <v>96.23699999999999</v>
       </c>
       <c r="G91">
         <v>19.5</v>
@@ -8749,37 +8749,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M91">
-        <v>22.44054366</v>
+        <v>22.6926846</v>
       </c>
       <c r="N91">
-        <v>-20.64054366</v>
+        <v>-20.8926846</v>
       </c>
       <c r="O91">
-        <v>-3.7152978588</v>
+        <v>-3.760683228</v>
       </c>
       <c r="P91">
-        <v>-16.9252458012</v>
+        <v>-17.132001372</v>
       </c>
       <c r="Q91">
-        <v>-6.525245801199999</v>
+        <v>-6.732001372000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5231776612064594</v>
+        <v>0.5709154273271052</v>
       </c>
       <c r="T91">
-        <v>8.049273179004595</v>
+        <v>8.854200496905055</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01443815287672936</v>
+        <v>0.01427772895587681</v>
       </c>
       <c r="W91">
-        <v>0.2323954835516672</v>
+        <v>0.2324333115122043</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08021196042627432</v>
+        <v>0.07932071642153782</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2662815230936944</v>
+        <v>0.2681815230936943</v>
       </c>
       <c r="C92">
-        <v>-43.50713919690506</v>
+        <v>-44.80843463120903</v>
       </c>
       <c r="D92">
-        <v>33.22986080309494</v>
+        <v>32.99786536879096</v>
       </c>
       <c r="E92">
-        <v>87.907</v>
+        <v>88.97629999999999</v>
       </c>
       <c r="F92">
-        <v>96.23699999999999</v>
+        <v>97.30629999999999</v>
       </c>
       <c r="G92">
         <v>19.5</v>
@@ -8831,37 +8831,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M92">
-        <v>22.6926846</v>
+        <v>22.94482554</v>
       </c>
       <c r="N92">
-        <v>-20.8926846</v>
+        <v>-21.14482554</v>
       </c>
       <c r="O92">
-        <v>-3.760683228</v>
+        <v>-3.8060685972</v>
       </c>
       <c r="P92">
-        <v>-17.132001372</v>
+        <v>-17.3387569428</v>
       </c>
       <c r="Q92">
-        <v>-6.732001372000001</v>
+        <v>-6.9387569428</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5709154273271052</v>
+        <v>0.6292615859190057</v>
       </c>
       <c r="T92">
-        <v>8.854200496905055</v>
+        <v>9.838000552116727</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01427772895587681</v>
+        <v>0.01412083083548256</v>
       </c>
       <c r="W92">
-        <v>0.2324333115122043</v>
+        <v>0.2324703080889932</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07932071642153782</v>
+        <v>0.07844906019712539</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2681815230936943</v>
+        <v>0.2700815230936943</v>
       </c>
       <c r="C93">
-        <v>-44.80843463120903</v>
+        <v>-46.10651315601726</v>
       </c>
       <c r="D93">
-        <v>32.99786536879096</v>
+        <v>32.76908684398273</v>
       </c>
       <c r="E93">
-        <v>88.97629999999999</v>
+        <v>90.04559999999999</v>
       </c>
       <c r="F93">
-        <v>97.30629999999999</v>
+        <v>98.37559999999999</v>
       </c>
       <c r="G93">
         <v>19.5</v>
@@ -8913,37 +8913,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M93">
-        <v>22.94482554</v>
+        <v>23.19696648</v>
       </c>
       <c r="N93">
-        <v>-21.14482554</v>
+        <v>-21.39696648</v>
       </c>
       <c r="O93">
-        <v>-3.8060685972</v>
+        <v>-3.8514539664</v>
       </c>
       <c r="P93">
-        <v>-17.3387569428</v>
+        <v>-17.5455125136</v>
       </c>
       <c r="Q93">
-        <v>-6.9387569428</v>
+        <v>-7.145512513600002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6292615859190057</v>
+        <v>0.7021942841588819</v>
       </c>
       <c r="T93">
-        <v>9.838000552116727</v>
+        <v>11.06775062113132</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01412083083548256</v>
+        <v>0.01396734354379253</v>
       </c>
       <c r="W93">
-        <v>0.2324703080889932</v>
+        <v>0.2325065003923737</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.07844906019712539</v>
+        <v>0.0775963530210696</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2700815230936943</v>
+        <v>0.2719815230936944</v>
       </c>
       <c r="C94">
-        <v>-46.10651315601726</v>
+        <v>-47.40144122039496</v>
       </c>
       <c r="D94">
-        <v>32.76908684398273</v>
+        <v>32.54345877960505</v>
       </c>
       <c r="E94">
-        <v>90.04559999999999</v>
+        <v>91.11490000000001</v>
       </c>
       <c r="F94">
-        <v>98.37559999999999</v>
+        <v>99.4449</v>
       </c>
       <c r="G94">
         <v>19.5</v>
@@ -8995,37 +8995,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M94">
-        <v>23.19696648</v>
+        <v>23.44910742</v>
       </c>
       <c r="N94">
-        <v>-21.39696648</v>
+        <v>-21.64910742</v>
       </c>
       <c r="O94">
-        <v>-3.8514539664</v>
+        <v>-3.8968393356</v>
       </c>
       <c r="P94">
-        <v>-17.5455125136</v>
+        <v>-17.7522680844</v>
       </c>
       <c r="Q94">
-        <v>-7.145512513600002</v>
+        <v>-7.3522680844</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7021942841588819</v>
+        <v>0.7959648961815793</v>
       </c>
       <c r="T94">
-        <v>11.06775062113132</v>
+        <v>12.64885785272151</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01396734354379253</v>
+        <v>0.01381715705407433</v>
       </c>
       <c r="W94">
-        <v>0.2325065003923737</v>
+        <v>0.2325419143666493</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.0775963530210696</v>
+        <v>0.07676198363374642</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2719815230936944</v>
+        <v>0.2738815230936943</v>
       </c>
       <c r="C95">
-        <v>-47.40144122039496</v>
+        <v>-48.69328345581024</v>
       </c>
       <c r="D95">
-        <v>32.54345877960505</v>
+        <v>32.32091654418976</v>
       </c>
       <c r="E95">
-        <v>91.11490000000001</v>
+        <v>92.1842</v>
       </c>
       <c r="F95">
-        <v>99.4449</v>
+        <v>100.5142</v>
       </c>
       <c r="G95">
         <v>19.5</v>
@@ -9077,37 +9077,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M95">
-        <v>23.44910742</v>
+        <v>23.70124836</v>
       </c>
       <c r="N95">
-        <v>-21.64910742</v>
+        <v>-21.90124836</v>
       </c>
       <c r="O95">
-        <v>-3.8968393356</v>
+        <v>-3.942224704800001</v>
       </c>
       <c r="P95">
-        <v>-17.7522680844</v>
+        <v>-17.9590236552</v>
       </c>
       <c r="Q95">
-        <v>-7.3522680844</v>
+        <v>-7.559023655200003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7959648961815793</v>
+        <v>0.9209923788785094</v>
       </c>
       <c r="T95">
-        <v>12.64885785272151</v>
+        <v>14.7570008281751</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01381715705407433</v>
+        <v>0.01367016602158418</v>
       </c>
       <c r="W95">
-        <v>0.2325419143666493</v>
+        <v>0.2325765748521104</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07676198363374642</v>
+        <v>0.07594536678657871</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2738815230936943</v>
+        <v>0.2757815230936944</v>
       </c>
       <c r="C96">
-        <v>-48.69328345581024</v>
+        <v>-49.98210273785867</v>
       </c>
       <c r="D96">
-        <v>32.32091654418976</v>
+        <v>32.10139726214133</v>
       </c>
       <c r="E96">
-        <v>92.1842</v>
+        <v>93.2535</v>
       </c>
       <c r="F96">
-        <v>100.5142</v>
+        <v>101.5835</v>
       </c>
       <c r="G96">
         <v>19.5</v>
@@ -9159,37 +9159,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M96">
-        <v>23.70124836</v>
+        <v>23.9533893</v>
       </c>
       <c r="N96">
-        <v>-21.90124836</v>
+        <v>-22.1533893</v>
       </c>
       <c r="O96">
-        <v>-3.942224704800001</v>
+        <v>-3.987610074</v>
       </c>
       <c r="P96">
-        <v>-17.9590236552</v>
+        <v>-18.165779226</v>
       </c>
       <c r="Q96">
-        <v>-7.559023655200003</v>
+        <v>-7.765779226000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9209923788785094</v>
+        <v>1.096030854654212</v>
       </c>
       <c r="T96">
-        <v>14.7570008281751</v>
+        <v>17.70840099381013</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01367016602158418</v>
+        <v>0.01352626953714645</v>
       </c>
       <c r="W96">
-        <v>0.2325765748521104</v>
+        <v>0.2326105056431409</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07594536678657871</v>
+        <v>0.07514594187303592</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2757815230936944</v>
+        <v>0.2776815230936943</v>
       </c>
       <c r="C97">
-        <v>-49.98210273785867</v>
+        <v>-51.26796024548904</v>
       </c>
       <c r="D97">
-        <v>32.10139726214133</v>
+        <v>31.88483975451097</v>
       </c>
       <c r="E97">
-        <v>93.2535</v>
+        <v>94.3228</v>
       </c>
       <c r="F97">
-        <v>101.5835</v>
+        <v>102.6528</v>
       </c>
       <c r="G97">
         <v>19.5</v>
@@ -9241,37 +9241,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M97">
-        <v>23.9533893</v>
+        <v>24.20553024</v>
       </c>
       <c r="N97">
-        <v>-22.1533893</v>
+        <v>-22.40553024</v>
       </c>
       <c r="O97">
-        <v>-3.987610074</v>
+        <v>-4.032995443200001</v>
       </c>
       <c r="P97">
-        <v>-18.165779226</v>
+        <v>-18.3725347968</v>
       </c>
       <c r="Q97">
-        <v>-7.765779226000001</v>
+        <v>-7.972534796800003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.096030854654212</v>
+        <v>1.358588568317765</v>
       </c>
       <c r="T97">
-        <v>17.70840099381013</v>
+        <v>22.13550124226267</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01352626953714645</v>
+        <v>0.01338537089613451</v>
       </c>
       <c r="W97">
-        <v>0.2326105056431409</v>
+        <v>0.2326437295426915</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07514594187303592</v>
+        <v>0.07436317164519168</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2776815230936943</v>
+        <v>0.2795815230936943</v>
       </c>
       <c r="C98">
-        <v>-51.26796024548902</v>
+        <v>-52.55091551784832</v>
       </c>
       <c r="D98">
-        <v>31.88483975451097</v>
+        <v>31.67118448215167</v>
       </c>
       <c r="E98">
-        <v>94.32279999999999</v>
+        <v>95.39209999999999</v>
       </c>
       <c r="F98">
-        <v>102.6528</v>
+        <v>103.7221</v>
       </c>
       <c r="G98">
         <v>19.5</v>
@@ -9323,37 +9323,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M98">
-        <v>24.20553024</v>
+        <v>24.45767118</v>
       </c>
       <c r="N98">
-        <v>-22.40553024</v>
+        <v>-22.65767118</v>
       </c>
       <c r="O98">
-        <v>-4.032995443199999</v>
+        <v>-4.0783808124</v>
       </c>
       <c r="P98">
-        <v>-18.3725347968</v>
+        <v>-18.5792903676</v>
       </c>
       <c r="Q98">
-        <v>-7.972534796799996</v>
+        <v>-8.179290367600002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.358588568317762</v>
+        <v>1.796184757757016</v>
       </c>
       <c r="T98">
-        <v>22.13550124226261</v>
+        <v>29.51400165635015</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01338537089613451</v>
+        <v>0.01324737738174137</v>
       </c>
       <c r="W98">
-        <v>0.2326437295426915</v>
+        <v>0.2326762684133854</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07436317164519179</v>
+        <v>0.07359654100967417</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2795815230936943</v>
+        <v>0.2814815230936943</v>
       </c>
       <c r="C99">
-        <v>-52.55091551784832</v>
+        <v>-53.83102650885619</v>
       </c>
       <c r="D99">
-        <v>31.67118448215167</v>
+        <v>31.46037349114381</v>
       </c>
       <c r="E99">
-        <v>95.39209999999999</v>
+        <v>96.4614</v>
       </c>
       <c r="F99">
-        <v>103.7221</v>
+        <v>104.7914</v>
       </c>
       <c r="G99">
         <v>19.5</v>
@@ -9405,37 +9405,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M99">
-        <v>24.45767118</v>
+        <v>24.70981212</v>
       </c>
       <c r="N99">
-        <v>-22.65767118</v>
+        <v>-22.90981212</v>
       </c>
       <c r="O99">
-        <v>-4.0783808124</v>
+        <v>-4.1237661816</v>
       </c>
       <c r="P99">
-        <v>-18.5792903676</v>
+        <v>-18.7860459384</v>
       </c>
       <c r="Q99">
-        <v>-8.179290367600002</v>
+        <v>-8.386045938399997</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.796184757757016</v>
+        <v>2.671377136635524</v>
       </c>
       <c r="T99">
-        <v>29.51400165635015</v>
+        <v>44.27100248452523</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01324737738174137</v>
+        <v>0.01311220006151952</v>
       </c>
       <c r="W99">
-        <v>0.2326762684133854</v>
+        <v>0.2327081432254937</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07359654100967417</v>
+        <v>0.07284555589733077</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2814815230936943</v>
+        <v>0.2833815230936944</v>
       </c>
       <c r="C100">
-        <v>-53.83102650885619</v>
+        <v>-55.1083496396144</v>
       </c>
       <c r="D100">
-        <v>31.46037349114381</v>
+        <v>31.25235036038559</v>
       </c>
       <c r="E100">
-        <v>96.4614</v>
+        <v>97.5307</v>
       </c>
       <c r="F100">
-        <v>104.7914</v>
+        <v>105.8607</v>
       </c>
       <c r="G100">
         <v>19.5</v>
@@ -9487,37 +9487,37 @@
         <v>1.799999999999999</v>
       </c>
       <c r="M100">
-        <v>24.70981212</v>
+        <v>24.96195306</v>
       </c>
       <c r="N100">
-        <v>-22.90981212</v>
+        <v>-23.16195306</v>
       </c>
       <c r="O100">
-        <v>-4.1237661816</v>
+        <v>-4.169151550800001</v>
       </c>
       <c r="P100">
-        <v>-18.7860459384</v>
+        <v>-18.9928015092</v>
       </c>
       <c r="Q100">
-        <v>-8.386045938399997</v>
+        <v>-8.592801509199999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.671377136635524</v>
+        <v>5.296954273271047</v>
       </c>
       <c r="T100">
-        <v>44.27100248452523</v>
+        <v>88.54200496905045</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01311220006151952</v>
+        <v>0.01297975359625165</v>
       </c>
       <c r="W100">
-        <v>0.2327081432254937</v>
+        <v>0.2327393741020038</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07284555589733077</v>
+        <v>0.07210974220139799</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2833815230936944</v>
-      </c>
-      <c r="C101">
-        <v>-55.1083496396144</v>
-      </c>
-      <c r="D101">
-        <v>31.25235036038559</v>
-      </c>
-      <c r="E101">
-        <v>97.5307</v>
-      </c>
-      <c r="F101">
-        <v>105.8607</v>
-      </c>
-      <c r="G101">
-        <v>19.5</v>
-      </c>
-      <c r="H101">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.2</v>
-      </c>
-      <c r="K101">
-        <v>10.4</v>
-      </c>
-      <c r="L101">
-        <v>1.799999999999999</v>
-      </c>
-      <c r="M101">
-        <v>24.96195306</v>
-      </c>
-      <c r="N101">
-        <v>-23.16195306</v>
-      </c>
-      <c r="O101">
-        <v>-4.169151550800001</v>
-      </c>
-      <c r="P101">
-        <v>-18.9928015092</v>
-      </c>
-      <c r="Q101">
-        <v>-8.592801509199999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.296954273271047</v>
-      </c>
-      <c r="T101">
-        <v>88.54200496905045</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01297975359625165</v>
-      </c>
-      <c r="W101">
-        <v>0.2327393741020038</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07210974220139799</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
